--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,34 +436,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -462,7 +474,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -475,7 +487,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -488,7 +500,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -501,7 +513,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -514,7 +526,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -527,7 +539,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -540,7 +552,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -553,7 +565,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -566,7 +578,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -579,7 +591,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -592,7 +604,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -605,7 +617,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -656,7 +668,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -690,7 +702,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -707,7 +719,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -741,7 +753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -775,7 +787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -792,7 +804,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -894,7 +906,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -928,7 +940,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -962,7 +974,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -996,7 +1008,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1030,7 +1042,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1047,7 +1059,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1064,7 +1076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1149,7 +1161,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1166,7 +1178,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1183,7 +1195,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1200,7 +1212,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1234,7 +1246,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1268,7 +1280,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1319,7 +1331,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1387,7 +1399,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1404,7 +1416,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1421,7 +1433,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1489,7 +1501,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1540,7 +1552,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1591,7 +1603,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1625,7 +1637,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1710,7 +1722,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1727,7 +1739,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1761,7 +1773,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1829,7 +1841,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1863,7 +1875,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1880,7 +1892,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1914,7 +1926,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1931,7 +1943,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -1999,7 +2011,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2067,7 +2079,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2135,7 +2147,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2203,7 +2215,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2254,7 +2266,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2288,7 +2300,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2305,7 +2317,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2339,7 +2351,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2424,7 +2436,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2458,7 +2470,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2526,7 +2538,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2560,7 +2572,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2628,7 +2640,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2645,7 +2657,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2662,7 +2674,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2679,7 +2691,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2696,7 +2708,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2747,7 +2759,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2798,7 +2810,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2866,7 +2878,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2883,7 +2895,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2951,7 +2963,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2968,7 +2980,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2985,7 +2997,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3104,7 +3116,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3121,7 +3133,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3138,7 +3150,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3155,7 +3167,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3172,7 +3184,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3189,7 +3201,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3206,7 +3218,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3274,7 +3286,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3291,7 +3303,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3342,7 +3354,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3359,7 +3371,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3393,7 +3405,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3410,7 +3422,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3461,7 +3473,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3529,7 +3541,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3546,7 +3558,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3614,7 +3626,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3631,7 +3643,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3648,7 +3660,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3682,7 +3694,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3784,7 +3796,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3801,7 +3813,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3818,7 +3830,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3886,7 +3898,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3903,7 +3915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3920,7 +3932,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3937,7 +3949,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3971,7 +3983,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -3988,7 +4000,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4107,7 +4119,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4141,7 +4153,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4158,7 +4170,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4175,7 +4187,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4192,7 +4204,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4277,7 +4289,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4294,7 +4306,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4328,7 +4340,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4345,7 +4357,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4379,7 +4391,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4413,7 +4425,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4464,7 +4476,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4515,7 +4527,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4566,7 +4578,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4600,7 +4612,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4651,7 +4663,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4685,7 +4697,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4719,7 +4731,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4753,7 +4765,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4770,7 +4782,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4787,7 +4799,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4804,7 +4816,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -4835,79 +4847,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4951,7 +4963,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -4995,7 +5007,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5039,7 +5051,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5083,7 +5095,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5127,7 +5139,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5171,7 +5183,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5215,7 +5227,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5259,7 +5271,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5303,7 +5315,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5347,7 +5359,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5391,7 +5403,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5435,7 +5447,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5479,7 +5491,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5523,7 +5535,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5611,7 +5623,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5655,7 +5667,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5743,7 +5755,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5787,7 +5799,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5831,7 +5843,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5875,7 +5887,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5963,7 +5975,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6051,7 +6063,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6095,7 +6107,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6139,7 +6151,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6183,7 +6195,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6227,7 +6239,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6271,7 +6283,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6315,7 +6327,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6359,7 +6371,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6403,7 +6415,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6447,7 +6459,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6491,7 +6503,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6535,7 +6547,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6623,7 +6635,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6667,7 +6679,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6711,7 +6723,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6755,7 +6767,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6799,7 +6811,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6887,7 +6899,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6931,7 +6943,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7019,7 +7031,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7063,7 +7075,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7107,7 +7119,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7151,7 +7163,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7195,7 +7207,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7239,7 +7251,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7327,7 +7339,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7371,7 +7383,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7415,7 +7427,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7459,7 +7471,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7503,7 +7515,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7547,7 +7559,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7591,7 +7603,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7635,7 +7647,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7679,7 +7691,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7723,7 +7735,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7767,7 +7779,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7811,7 +7823,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7855,7 +7867,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7899,7 +7911,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7943,7 +7955,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7987,7 +7999,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8031,7 +8043,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8075,7 +8087,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8119,7 +8131,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8163,7 +8175,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8207,7 +8219,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8251,7 +8263,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8295,7 +8307,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8339,7 +8351,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8383,7 +8395,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8427,7 +8439,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8471,7 +8483,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8515,7 +8527,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8603,7 +8615,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8647,7 +8659,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8691,7 +8703,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8735,7 +8747,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8779,7 +8791,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8823,7 +8835,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8867,7 +8879,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8955,7 +8967,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -8999,7 +9011,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9043,7 +9055,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9087,7 +9099,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9131,7 +9143,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9175,7 +9187,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9219,7 +9231,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9263,7 +9275,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9307,7 +9319,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9351,7 +9363,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9395,7 +9407,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9439,7 +9451,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9483,7 +9495,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9527,7 +9539,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9571,7 +9583,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9615,7 +9627,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9659,7 +9671,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9703,7 +9715,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9747,7 +9759,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9791,7 +9803,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9879,7 +9891,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9923,7 +9935,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9967,7 +9979,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -10011,7 +10023,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10055,7 +10067,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10099,7 +10111,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10143,7 +10155,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10187,7 +10199,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10231,7 +10243,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10275,7 +10287,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10319,7 +10331,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10363,7 +10375,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10407,7 +10419,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10451,7 +10463,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10495,7 +10507,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10539,7 +10551,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10583,7 +10595,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10627,7 +10639,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10671,7 +10683,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10715,7 +10727,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10759,7 +10771,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10803,7 +10815,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10847,7 +10859,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10891,7 +10903,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10935,7 +10947,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11023,7 +11035,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11067,7 +11079,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11155,7 +11167,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11199,7 +11211,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11243,7 +11255,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11287,7 +11299,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11331,7 +11343,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11375,7 +11387,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11419,7 +11431,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11463,7 +11475,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11507,7 +11519,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11551,7 +11563,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11595,7 +11607,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11639,7 +11651,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11683,7 +11695,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11727,7 +11739,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11771,7 +11783,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11815,7 +11827,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11859,7 +11871,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11903,7 +11915,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11947,7 +11959,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -11991,7 +12003,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12035,7 +12047,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12079,7 +12091,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12123,7 +12135,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12167,7 +12179,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12211,7 +12223,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12255,7 +12267,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12299,7 +12311,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12343,7 +12355,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12431,7 +12443,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12475,7 +12487,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12519,7 +12531,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12563,7 +12575,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12607,7 +12619,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12651,7 +12663,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12695,7 +12707,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12739,7 +12751,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12783,7 +12795,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12827,7 +12839,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12871,7 +12883,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12915,7 +12927,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12959,7 +12971,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -13003,7 +13015,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13091,7 +13103,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13135,7 +13147,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13179,7 +13191,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13223,7 +13235,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13267,7 +13279,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13311,7 +13323,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13355,7 +13367,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13399,7 +13411,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13443,7 +13455,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13487,7 +13499,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13531,7 +13543,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13575,7 +13587,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13619,7 +13631,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13707,7 +13719,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13751,7 +13763,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13795,7 +13807,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13839,7 +13851,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13883,7 +13895,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13927,7 +13939,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13971,7 +13983,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -14015,7 +14027,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14059,7 +14071,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14103,7 +14115,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14147,7 +14159,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14191,7 +14203,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14235,7 +14247,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14279,7 +14291,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14323,7 +14335,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14367,7 +14379,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14411,7 +14423,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14455,7 +14467,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14499,7 +14511,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14543,7 +14555,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14587,7 +14599,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14631,7 +14643,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14675,7 +14687,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14719,7 +14731,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14763,7 +14775,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14807,7 +14819,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14851,7 +14863,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14895,7 +14907,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14983,7 +14995,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15027,7 +15039,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15071,7 +15083,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15159,7 +15171,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15203,7 +15215,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15247,7 +15259,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15291,7 +15303,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15335,7 +15347,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15379,7 +15391,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15423,7 +15435,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15467,7 +15479,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15511,7 +15523,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15555,7 +15567,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15599,7 +15611,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15643,7 +15655,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15687,7 +15699,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15731,7 +15743,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15775,7 +15787,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15819,7 +15831,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15863,7 +15875,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15907,7 +15919,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15951,7 +15963,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -15995,7 +16007,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16039,7 +16051,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16083,7 +16095,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16127,7 +16139,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16171,7 +16183,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16259,7 +16271,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16303,7 +16315,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -16361,79 +16373,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16451,7 +16463,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16469,7 +16481,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16487,7 +16499,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16505,7 +16517,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16523,7 +16535,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16541,7 +16553,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16559,7 +16571,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16577,7 +16589,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16595,7 +16607,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16613,7 +16625,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16631,7 +16643,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16649,7 +16661,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16693,7 +16705,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16781,7 +16793,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16825,7 +16837,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16869,7 +16881,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16913,7 +16925,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16957,7 +16969,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -17001,7 +17013,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -17045,7 +17057,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17089,7 +17101,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17133,7 +17145,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17177,7 +17189,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17221,7 +17233,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17265,7 +17277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17309,7 +17321,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17353,7 +17365,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17397,7 +17409,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17441,7 +17453,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17485,7 +17497,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17529,7 +17541,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17573,7 +17585,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17617,7 +17629,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17661,7 +17673,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17705,7 +17717,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17749,7 +17761,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17793,7 +17805,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17837,7 +17849,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17881,7 +17893,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17925,7 +17937,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17969,7 +17981,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -18013,7 +18025,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -18057,7 +18069,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18101,7 +18113,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18145,7 +18157,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18189,7 +18201,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18233,7 +18245,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18277,7 +18289,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18321,7 +18333,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18365,7 +18377,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18409,7 +18421,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18453,7 +18465,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18497,7 +18509,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18541,7 +18553,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18585,7 +18597,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18629,7 +18641,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18673,7 +18685,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18717,7 +18729,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18761,7 +18773,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18805,7 +18817,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18849,7 +18861,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18893,7 +18905,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18937,7 +18949,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18981,7 +18993,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -19025,7 +19037,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19069,7 +19081,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19113,7 +19125,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19157,7 +19169,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19201,7 +19213,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19245,7 +19257,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19289,7 +19301,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19333,7 +19345,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19377,7 +19389,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19421,7 +19433,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19465,7 +19477,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19509,7 +19521,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19553,7 +19565,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19597,7 +19609,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19641,7 +19653,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19685,7 +19697,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19729,7 +19741,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19773,7 +19785,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19817,7 +19829,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19861,7 +19873,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19905,7 +19917,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19949,7 +19961,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -19993,7 +20005,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -20037,7 +20049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20081,7 +20093,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20125,7 +20137,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20169,7 +20181,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20213,7 +20225,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20257,7 +20269,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20301,7 +20313,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20345,7 +20357,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20389,7 +20401,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20433,7 +20445,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20477,7 +20489,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20521,7 +20533,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20565,7 +20577,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20609,7 +20621,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20653,7 +20665,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20697,7 +20709,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20741,7 +20753,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20785,7 +20797,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20829,7 +20841,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20873,7 +20885,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20917,7 +20929,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20961,7 +20973,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -21005,7 +21017,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -21049,7 +21061,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21093,7 +21105,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21137,7 +21149,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21181,7 +21193,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21225,7 +21237,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21269,7 +21281,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21313,7 +21325,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21357,7 +21369,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21401,7 +21413,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21445,7 +21457,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21489,7 +21501,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21533,7 +21545,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21577,7 +21589,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21621,7 +21633,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21665,7 +21677,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21709,7 +21721,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21753,7 +21765,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21797,7 +21809,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21841,7 +21853,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21885,7 +21897,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21929,7 +21941,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21973,7 +21985,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -22017,7 +22029,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22061,7 +22073,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22105,7 +22117,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22149,7 +22161,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22193,7 +22205,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22237,7 +22249,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22281,7 +22293,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22325,7 +22337,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22369,7 +22381,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22413,7 +22425,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22457,7 +22469,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22501,7 +22513,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22545,7 +22557,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22589,7 +22601,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22633,7 +22645,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22677,7 +22689,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22721,7 +22733,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22765,7 +22777,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22809,7 +22821,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22853,7 +22865,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22897,7 +22909,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22941,7 +22953,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22985,7 +22997,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -23029,7 +23041,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23073,7 +23085,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23117,7 +23129,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23161,7 +23173,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23205,7 +23217,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23249,7 +23261,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23293,7 +23305,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23337,7 +23349,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23381,7 +23393,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23425,7 +23437,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23469,7 +23481,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23513,7 +23525,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23557,7 +23569,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23601,7 +23613,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23645,7 +23657,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23689,7 +23701,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23733,7 +23745,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23777,7 +23789,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23821,7 +23833,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23865,7 +23877,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23909,7 +23921,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23953,7 +23965,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -23997,7 +24009,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -24041,7 +24053,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24085,7 +24097,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24129,7 +24141,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24173,7 +24185,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24217,7 +24229,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24261,7 +24273,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24305,7 +24317,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24349,7 +24361,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24393,7 +24405,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24437,7 +24449,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24481,7 +24493,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24525,7 +24537,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24569,7 +24581,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24613,7 +24625,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24657,7 +24669,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24701,7 +24713,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24745,7 +24757,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24789,7 +24801,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24833,7 +24845,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24877,7 +24889,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24921,7 +24933,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24965,7 +24977,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -25009,7 +25021,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -25053,7 +25065,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25097,7 +25109,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25141,7 +25153,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25185,7 +25197,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25229,7 +25241,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25273,7 +25285,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25317,7 +25329,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25361,7 +25373,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25405,7 +25417,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25449,7 +25461,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25493,7 +25505,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25537,7 +25549,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25581,7 +25593,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25625,7 +25637,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25669,7 +25681,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25713,7 +25725,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25757,7 +25769,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25801,7 +25813,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25845,7 +25857,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25889,7 +25901,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25933,7 +25945,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25977,7 +25989,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -26021,7 +26033,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26065,7 +26077,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26109,7 +26121,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26153,7 +26165,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26197,7 +26209,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26241,7 +26253,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26285,7 +26297,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26329,7 +26341,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26373,7 +26385,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26417,7 +26429,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26461,7 +26473,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26505,7 +26517,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26549,7 +26561,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26593,7 +26605,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26637,7 +26649,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26681,7 +26693,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26725,7 +26737,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26769,7 +26781,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26813,7 +26825,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26857,7 +26869,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26901,7 +26913,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26945,7 +26957,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -26989,7 +27001,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -27033,7 +27045,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27077,7 +27089,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27121,7 +27133,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27165,7 +27177,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27209,7 +27221,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27253,7 +27265,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27297,7 +27309,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27341,7 +27353,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27385,7 +27397,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27429,7 +27441,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27473,7 +27485,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27517,7 +27529,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -27575,32 +27587,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,34 +424,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -474,7 +462,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -487,7 +475,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -500,7 +488,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -513,7 +501,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -526,7 +514,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -539,7 +527,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -552,7 +540,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -565,7 +553,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -578,7 +566,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -591,7 +579,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -604,7 +592,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -617,7 +605,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -668,7 +656,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -702,7 +690,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -719,7 +707,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -736,7 +724,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -753,7 +741,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -787,7 +775,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -804,7 +792,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -872,7 +860,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -889,7 +877,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -906,7 +894,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -923,7 +911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -940,7 +928,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -974,7 +962,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1008,7 +996,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1025,7 +1013,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1042,7 +1030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1059,7 +1047,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1076,7 +1064,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1161,7 +1149,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1178,7 +1166,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1195,7 +1183,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1212,7 +1200,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1246,7 +1234,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1280,7 +1268,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1297,7 +1285,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1314,7 +1302,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1331,7 +1319,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1348,7 +1336,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1365,7 +1353,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1382,7 +1370,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1399,7 +1387,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1416,7 +1404,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1433,7 +1421,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1484,7 +1472,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1501,7 +1489,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1518,7 +1506,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1535,7 +1523,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1552,7 +1540,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1569,7 +1557,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1586,7 +1574,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1603,7 +1591,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1620,7 +1608,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1671,7 +1659,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1688,7 +1676,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1705,7 +1693,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1722,7 +1710,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1739,7 +1727,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1773,7 +1761,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1790,7 +1778,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1824,7 +1812,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1841,7 +1829,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1858,7 +1846,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1875,7 +1863,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1892,7 +1880,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1909,7 +1897,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1926,7 +1914,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1943,7 +1931,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1960,7 +1948,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1977,7 +1965,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1994,7 +1982,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -2011,7 +1999,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2028,7 +2016,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2045,7 +2033,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2062,7 +2050,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2079,7 +2067,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2096,7 +2084,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2113,7 +2101,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2147,7 +2135,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2164,7 +2152,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2181,7 +2169,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2198,7 +2186,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2215,7 +2203,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2232,7 +2220,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2266,7 +2254,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2283,7 +2271,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2300,7 +2288,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2317,7 +2305,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2334,7 +2322,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2351,7 +2339,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2368,7 +2356,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2385,7 +2373,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2402,7 +2390,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2419,7 +2407,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2436,7 +2424,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2470,7 +2458,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2487,7 +2475,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2504,7 +2492,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2521,7 +2509,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2555,7 +2543,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2572,7 +2560,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2606,7 +2594,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2623,7 +2611,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2640,7 +2628,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2657,7 +2645,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2674,7 +2662,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2691,7 +2679,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2708,7 +2696,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2725,7 +2713,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2759,7 +2747,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2776,7 +2764,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2793,7 +2781,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2810,7 +2798,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2827,7 +2815,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2861,7 +2849,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2878,7 +2866,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2895,7 +2883,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2912,7 +2900,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2929,7 +2917,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2946,7 +2934,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2963,7 +2951,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2980,7 +2968,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2997,7 +2985,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3031,7 +3019,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3065,7 +3053,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3082,7 +3070,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3099,7 +3087,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3116,7 +3104,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3133,7 +3121,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3150,7 +3138,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3167,7 +3155,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3184,7 +3172,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3201,7 +3189,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3218,7 +3206,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3269,7 +3257,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3286,7 +3274,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3303,7 +3291,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3320,7 +3308,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3354,7 +3342,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3371,7 +3359,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3388,7 +3376,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3405,7 +3393,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3422,7 +3410,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3439,7 +3427,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3456,7 +3444,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3473,7 +3461,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3490,7 +3478,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3507,7 +3495,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3524,7 +3512,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3541,7 +3529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3558,7 +3546,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3575,7 +3563,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3592,7 +3580,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3609,7 +3597,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3626,7 +3614,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3643,7 +3631,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3660,7 +3648,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3677,7 +3665,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3694,7 +3682,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3711,7 +3699,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3745,7 +3733,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3762,7 +3750,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3779,7 +3767,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3796,7 +3784,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3813,7 +3801,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3830,7 +3818,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3864,7 +3852,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3881,7 +3869,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3915,7 +3903,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3932,7 +3920,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3949,7 +3937,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3966,7 +3954,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3983,7 +3971,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -4000,7 +3988,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4017,7 +4005,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4034,7 +4022,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4068,7 +4056,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4102,7 +4090,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4119,7 +4107,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4136,7 +4124,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4153,7 +4141,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4170,7 +4158,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4187,7 +4175,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4204,7 +4192,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4238,7 +4226,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4255,7 +4243,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4272,7 +4260,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4289,7 +4277,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4306,7 +4294,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4323,7 +4311,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4340,7 +4328,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4357,7 +4345,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4374,7 +4362,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4391,7 +4379,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4408,7 +4396,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4425,7 +4413,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4442,7 +4430,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4459,7 +4447,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4476,7 +4464,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4493,7 +4481,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4510,7 +4498,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4527,7 +4515,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4544,7 +4532,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4561,7 +4549,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4578,7 +4566,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4595,7 +4583,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4612,7 +4600,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4629,7 +4617,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4663,7 +4651,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4680,7 +4668,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4697,7 +4685,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4731,7 +4719,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4748,7 +4736,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4765,7 +4753,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4782,7 +4770,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4799,7 +4787,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4816,7 +4804,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -4847,79 +4835,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4963,7 +4951,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -5007,7 +4995,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5051,7 +5039,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5095,7 +5083,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5139,7 +5127,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5183,7 +5171,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5227,7 +5215,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5271,7 +5259,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5315,7 +5303,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5359,7 +5347,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5403,7 +5391,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5447,7 +5435,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5491,7 +5479,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5535,7 +5523,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5579,7 +5567,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5623,7 +5611,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5667,7 +5655,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5711,7 +5699,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5755,7 +5743,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5799,7 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5843,7 +5831,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5887,7 +5875,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5931,7 +5919,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5975,7 +5963,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6063,7 +6051,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6107,7 +6095,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6151,7 +6139,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6195,7 +6183,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6239,7 +6227,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6283,7 +6271,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6327,7 +6315,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6371,7 +6359,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6415,7 +6403,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6459,7 +6447,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6503,7 +6491,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6547,7 +6535,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6591,7 +6579,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6635,7 +6623,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6679,7 +6667,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6723,7 +6711,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6767,7 +6755,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6811,7 +6799,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6899,7 +6887,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6943,7 +6931,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6987,7 +6975,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7031,7 +7019,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7075,7 +7063,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7119,7 +7107,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7163,7 +7151,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7207,7 +7195,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7251,7 +7239,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7339,7 +7327,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7383,7 +7371,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7427,7 +7415,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7471,7 +7459,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7515,7 +7503,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7559,7 +7547,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7603,7 +7591,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7647,7 +7635,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7691,7 +7679,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7735,7 +7723,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7779,7 +7767,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7823,7 +7811,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7867,7 +7855,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7911,7 +7899,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7955,7 +7943,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -7999,7 +7987,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8043,7 +8031,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8087,7 +8075,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8131,7 +8119,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8175,7 +8163,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8219,7 +8207,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8263,7 +8251,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8307,7 +8295,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8351,7 +8339,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8395,7 +8383,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8439,7 +8427,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8483,7 +8471,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8527,7 +8515,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8615,7 +8603,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8659,7 +8647,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8703,7 +8691,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8747,7 +8735,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8791,7 +8779,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8835,7 +8823,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8879,7 +8867,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8967,7 +8955,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -9011,7 +8999,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9055,7 +9043,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9099,7 +9087,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9143,7 +9131,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9187,7 +9175,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9231,7 +9219,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9275,7 +9263,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9319,7 +9307,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9363,7 +9351,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9407,7 +9395,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9451,7 +9439,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9495,7 +9483,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9539,7 +9527,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9583,7 +9571,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9627,7 +9615,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9671,7 +9659,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9715,7 +9703,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9759,7 +9747,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9803,7 +9791,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9891,7 +9879,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9935,7 +9923,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9979,7 +9967,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -10023,7 +10011,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10067,7 +10055,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10111,7 +10099,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10155,7 +10143,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10199,7 +10187,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10243,7 +10231,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10287,7 +10275,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10331,7 +10319,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10375,7 +10363,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10419,7 +10407,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10463,7 +10451,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10507,7 +10495,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10551,7 +10539,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10595,7 +10583,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10639,7 +10627,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10683,7 +10671,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10727,7 +10715,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10771,7 +10759,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10815,7 +10803,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10859,7 +10847,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10903,7 +10891,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10947,7 +10935,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11035,7 +11023,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11079,7 +11067,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11167,7 +11155,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11211,7 +11199,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11255,7 +11243,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11299,7 +11287,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11343,7 +11331,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11387,7 +11375,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11431,7 +11419,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11475,7 +11463,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11519,7 +11507,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11563,7 +11551,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11607,7 +11595,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11651,7 +11639,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11695,7 +11683,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11739,7 +11727,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11783,7 +11771,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11827,7 +11815,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11871,7 +11859,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11915,7 +11903,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11959,7 +11947,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -12003,7 +11991,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12047,7 +12035,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12091,7 +12079,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12135,7 +12123,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12179,7 +12167,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12223,7 +12211,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12267,7 +12255,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12311,7 +12299,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12355,7 +12343,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12443,7 +12431,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12487,7 +12475,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12531,7 +12519,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12575,7 +12563,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12619,7 +12607,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12663,7 +12651,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12707,7 +12695,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12751,7 +12739,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12795,7 +12783,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12839,7 +12827,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12883,7 +12871,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12927,7 +12915,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12971,7 +12959,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -13015,7 +13003,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13103,7 +13091,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13147,7 +13135,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13191,7 +13179,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13235,7 +13223,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13279,7 +13267,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13323,7 +13311,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13367,7 +13355,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13411,7 +13399,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13455,7 +13443,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13499,7 +13487,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13543,7 +13531,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13587,7 +13575,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13631,7 +13619,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13719,7 +13707,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13763,7 +13751,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13807,7 +13795,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13851,7 +13839,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13895,7 +13883,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13939,7 +13927,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13983,7 +13971,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -14027,7 +14015,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14071,7 +14059,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14115,7 +14103,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14159,7 +14147,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14203,7 +14191,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14247,7 +14235,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14291,7 +14279,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14335,7 +14323,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14379,7 +14367,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14423,7 +14411,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14467,7 +14455,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14511,7 +14499,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14555,7 +14543,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14599,7 +14587,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14643,7 +14631,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14687,7 +14675,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14731,7 +14719,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14775,7 +14763,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14819,7 +14807,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14863,7 +14851,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14907,7 +14895,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -14995,7 +14983,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15039,7 +15027,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15083,7 +15071,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15171,7 +15159,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15215,7 +15203,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15259,7 +15247,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15303,7 +15291,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15347,7 +15335,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15391,7 +15379,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15435,7 +15423,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15479,7 +15467,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15523,7 +15511,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15567,7 +15555,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15611,7 +15599,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15655,7 +15643,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15699,7 +15687,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15743,7 +15731,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15787,7 +15775,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15831,7 +15819,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15875,7 +15863,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15919,7 +15907,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15963,7 +15951,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -16007,7 +15995,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16051,7 +16039,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16095,7 +16083,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16139,7 +16127,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16183,7 +16171,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16271,7 +16259,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16315,7 +16303,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -16373,79 +16361,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16463,7 +16451,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16481,7 +16469,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16499,7 +16487,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16517,7 +16505,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16535,7 +16523,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16553,7 +16541,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16571,7 +16559,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16589,7 +16577,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16607,7 +16595,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16625,7 +16613,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16643,7 +16631,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16661,7 +16649,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16705,7 +16693,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16793,7 +16781,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16837,7 +16825,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16881,7 +16869,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16925,7 +16913,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -16969,7 +16957,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -17013,7 +17001,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -17057,7 +17045,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17101,7 +17089,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17145,7 +17133,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17189,7 +17177,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17233,7 +17221,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17277,7 +17265,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17321,7 +17309,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17365,7 +17353,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17409,7 +17397,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17453,7 +17441,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17497,7 +17485,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17541,7 +17529,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17585,7 +17573,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17629,7 +17617,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17673,7 +17661,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17717,7 +17705,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17761,7 +17749,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17805,7 +17793,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17849,7 +17837,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17893,7 +17881,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17937,7 +17925,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -17981,7 +17969,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -18025,7 +18013,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -18069,7 +18057,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18113,7 +18101,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18157,7 +18145,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18201,7 +18189,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18245,7 +18233,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18289,7 +18277,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18333,7 +18321,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18377,7 +18365,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18421,7 +18409,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18465,7 +18453,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18509,7 +18497,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18553,7 +18541,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18597,7 +18585,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18641,7 +18629,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18685,7 +18673,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18729,7 +18717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18773,7 +18761,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18817,7 +18805,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18861,7 +18849,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18905,7 +18893,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18949,7 +18937,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -18993,7 +18981,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -19037,7 +19025,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19081,7 +19069,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19125,7 +19113,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19169,7 +19157,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19213,7 +19201,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19257,7 +19245,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19301,7 +19289,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19345,7 +19333,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19389,7 +19377,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19433,7 +19421,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19477,7 +19465,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19521,7 +19509,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19565,7 +19553,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19609,7 +19597,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19653,7 +19641,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19697,7 +19685,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19741,7 +19729,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19785,7 +19773,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19829,7 +19817,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19873,7 +19861,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19917,7 +19905,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -19961,7 +19949,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -20005,7 +19993,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -20049,7 +20037,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20093,7 +20081,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20137,7 +20125,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20181,7 +20169,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20225,7 +20213,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20269,7 +20257,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20313,7 +20301,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20357,7 +20345,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20401,7 +20389,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20445,7 +20433,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20489,7 +20477,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20533,7 +20521,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20577,7 +20565,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20621,7 +20609,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20665,7 +20653,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20709,7 +20697,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20753,7 +20741,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20797,7 +20785,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20841,7 +20829,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20885,7 +20873,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20929,7 +20917,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -20973,7 +20961,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -21017,7 +21005,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -21061,7 +21049,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21105,7 +21093,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21149,7 +21137,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21193,7 +21181,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21237,7 +21225,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21281,7 +21269,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21325,7 +21313,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21369,7 +21357,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21413,7 +21401,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21457,7 +21445,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21501,7 +21489,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21545,7 +21533,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21589,7 +21577,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21633,7 +21621,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21677,7 +21665,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21721,7 +21709,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21765,7 +21753,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21809,7 +21797,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21853,7 +21841,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21897,7 +21885,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21941,7 +21929,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -21985,7 +21973,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -22029,7 +22017,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22073,7 +22061,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22117,7 +22105,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22161,7 +22149,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22205,7 +22193,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22249,7 +22237,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22293,7 +22281,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22337,7 +22325,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22381,7 +22369,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22425,7 +22413,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22469,7 +22457,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22513,7 +22501,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22557,7 +22545,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22601,7 +22589,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22645,7 +22633,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22689,7 +22677,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22733,7 +22721,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22777,7 +22765,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22821,7 +22809,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22865,7 +22853,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22909,7 +22897,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -22953,7 +22941,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -22997,7 +22985,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -23041,7 +23029,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23085,7 +23073,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23129,7 +23117,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23173,7 +23161,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23217,7 +23205,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23261,7 +23249,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23305,7 +23293,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23349,7 +23337,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23393,7 +23381,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23437,7 +23425,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23481,7 +23469,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23525,7 +23513,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23569,7 +23557,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23613,7 +23601,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23657,7 +23645,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23701,7 +23689,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23745,7 +23733,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23789,7 +23777,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23833,7 +23821,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23877,7 +23865,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23921,7 +23909,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -23965,7 +23953,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -24009,7 +23997,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -24053,7 +24041,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24097,7 +24085,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24141,7 +24129,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24185,7 +24173,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24229,7 +24217,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24273,7 +24261,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24317,7 +24305,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24361,7 +24349,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24405,7 +24393,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24449,7 +24437,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24493,7 +24481,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24537,7 +24525,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24581,7 +24569,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24625,7 +24613,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24669,7 +24657,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24713,7 +24701,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24757,7 +24745,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24801,7 +24789,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24845,7 +24833,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24889,7 +24877,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24933,7 +24921,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -24977,7 +24965,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -25021,7 +25009,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -25065,7 +25053,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25109,7 +25097,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25153,7 +25141,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25197,7 +25185,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25241,7 +25229,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25285,7 +25273,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25329,7 +25317,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25373,7 +25361,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25417,7 +25405,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25461,7 +25449,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25505,7 +25493,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25549,7 +25537,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25593,7 +25581,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25637,7 +25625,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25681,7 +25669,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25725,7 +25713,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25769,7 +25757,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25813,7 +25801,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25857,7 +25845,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25901,7 +25889,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25945,7 +25933,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -25989,7 +25977,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -26033,7 +26021,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26077,7 +26065,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26121,7 +26109,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26165,7 +26153,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26209,7 +26197,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26253,7 +26241,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26297,7 +26285,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26341,7 +26329,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26385,7 +26373,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26429,7 +26417,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26473,7 +26461,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26517,7 +26505,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26561,7 +26549,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26605,7 +26593,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26649,7 +26637,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26693,7 +26681,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26737,7 +26725,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26781,7 +26769,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26825,7 +26813,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26869,7 +26857,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26913,7 +26901,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -26957,7 +26945,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -27001,7 +26989,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -27045,7 +27033,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27089,7 +27077,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27133,7 +27121,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27177,7 +27165,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27221,7 +27209,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27265,7 +27253,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27309,7 +27297,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27353,7 +27341,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27397,7 +27385,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27441,7 +27429,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27485,7 +27473,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27529,7 +27517,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -27587,32 +27575,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,34 +424,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -474,7 +462,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -487,7 +475,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -500,7 +488,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -513,7 +501,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -526,7 +514,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -539,7 +527,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -552,7 +540,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -565,7 +553,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -578,7 +566,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -591,7 +579,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -604,7 +592,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -617,7 +605,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -634,7 +622,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -668,7 +656,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -702,7 +690,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -719,7 +707,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -736,7 +724,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -753,7 +741,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -787,7 +775,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -804,7 +792,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -872,7 +860,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -889,7 +877,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -906,7 +894,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -923,7 +911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -940,7 +928,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -974,7 +962,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1008,7 +996,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1025,7 +1013,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1042,7 +1030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1059,7 +1047,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1076,7 +1064,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1110,7 +1098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1161,7 +1149,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1178,7 +1166,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1195,7 +1183,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1212,7 +1200,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1246,7 +1234,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1280,7 +1268,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1297,7 +1285,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1314,7 +1302,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1331,7 +1319,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1348,7 +1336,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1365,7 +1353,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1382,7 +1370,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1399,7 +1387,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1416,7 +1404,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1433,7 +1421,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1484,7 +1472,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1501,7 +1489,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1518,7 +1506,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1535,7 +1523,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1552,7 +1540,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1569,7 +1557,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1586,7 +1574,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1603,7 +1591,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1620,7 +1608,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1671,7 +1659,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1688,7 +1676,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1705,7 +1693,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1722,7 +1710,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1739,7 +1727,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1773,7 +1761,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1790,7 +1778,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1824,7 +1812,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1841,7 +1829,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1858,7 +1846,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1875,7 +1863,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1892,7 +1880,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1909,7 +1897,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1926,7 +1914,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1943,7 +1931,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1960,7 +1948,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1977,7 +1965,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1994,7 +1982,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -2011,7 +1999,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2028,7 +2016,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2045,7 +2033,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2062,7 +2050,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2079,7 +2067,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2096,7 +2084,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2113,7 +2101,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2147,7 +2135,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2164,7 +2152,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2181,7 +2169,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2198,7 +2186,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2215,7 +2203,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2232,7 +2220,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2266,7 +2254,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2283,7 +2271,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2300,7 +2288,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2317,7 +2305,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2334,7 +2322,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2351,7 +2339,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2368,7 +2356,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2385,7 +2373,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2402,7 +2390,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2419,7 +2407,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2436,7 +2424,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2470,7 +2458,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2487,7 +2475,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2504,7 +2492,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2521,7 +2509,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2555,7 +2543,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2572,7 +2560,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2606,7 +2594,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2623,7 +2611,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2640,7 +2628,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2657,7 +2645,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2674,7 +2662,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2691,7 +2679,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2708,7 +2696,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2725,7 +2713,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2759,7 +2747,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2776,7 +2764,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2793,7 +2781,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2810,7 +2798,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2827,7 +2815,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2861,7 +2849,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2878,7 +2866,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2895,7 +2883,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2912,7 +2900,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2929,7 +2917,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2946,7 +2934,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2963,7 +2951,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2980,7 +2968,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2997,7 +2985,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3031,7 +3019,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3065,7 +3053,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3082,7 +3070,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3099,7 +3087,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3116,7 +3104,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3133,7 +3121,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3150,7 +3138,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3167,7 +3155,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3184,7 +3172,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3201,7 +3189,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3218,7 +3206,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3269,7 +3257,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3286,7 +3274,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3303,7 +3291,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3320,7 +3308,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3354,7 +3342,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3371,7 +3359,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3388,7 +3376,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3405,7 +3393,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3422,7 +3410,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3439,7 +3427,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3456,7 +3444,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3473,7 +3461,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3490,7 +3478,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3507,7 +3495,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3524,7 +3512,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3541,7 +3529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3558,7 +3546,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3575,7 +3563,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3592,7 +3580,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3609,7 +3597,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3626,7 +3614,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3643,7 +3631,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3660,7 +3648,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3677,7 +3665,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3694,7 +3682,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3711,7 +3699,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3745,7 +3733,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3762,7 +3750,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3779,7 +3767,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3796,7 +3784,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3813,7 +3801,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3830,7 +3818,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3864,7 +3852,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3881,7 +3869,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3915,7 +3903,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3932,7 +3920,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3949,7 +3937,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3966,7 +3954,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3983,7 +3971,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -4000,7 +3988,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4017,7 +4005,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4034,7 +4022,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4068,7 +4056,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4102,7 +4090,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4119,7 +4107,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4136,7 +4124,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4153,7 +4141,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4170,7 +4158,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4187,7 +4175,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4204,7 +4192,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4238,7 +4226,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4255,7 +4243,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4272,7 +4260,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4289,7 +4277,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4306,7 +4294,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4323,7 +4311,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4340,7 +4328,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4357,7 +4345,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4374,7 +4362,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4391,7 +4379,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4408,7 +4396,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4425,7 +4413,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4442,7 +4430,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4459,7 +4447,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4476,7 +4464,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4493,7 +4481,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4510,7 +4498,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4527,7 +4515,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4544,7 +4532,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4561,7 +4549,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4578,7 +4566,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4595,7 +4583,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4612,7 +4600,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4629,7 +4617,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4663,7 +4651,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4680,7 +4668,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4697,7 +4685,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4731,7 +4719,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4748,7 +4736,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4765,7 +4753,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4782,7 +4770,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4799,7 +4787,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4816,7 +4804,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -4833,7 +4821,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -4864,79 +4852,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4980,7 +4968,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -5024,7 +5012,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5068,7 +5056,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5112,7 +5100,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5156,7 +5144,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5200,7 +5188,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5244,7 +5232,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5288,7 +5276,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5332,7 +5320,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5376,7 +5364,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5420,7 +5408,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5464,7 +5452,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5508,7 +5496,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5552,7 +5540,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5596,7 +5584,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5640,7 +5628,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5684,7 +5672,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5728,7 +5716,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5772,7 +5760,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5860,7 +5848,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5904,7 +5892,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5948,7 +5936,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5992,7 +5980,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -6036,7 +6024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6080,7 +6068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6124,7 +6112,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6168,7 +6156,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6212,7 +6200,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6256,7 +6244,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6300,7 +6288,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6344,7 +6332,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6388,7 +6376,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6476,7 +6464,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6520,7 +6508,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6564,7 +6552,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6608,7 +6596,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6652,7 +6640,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6696,7 +6684,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6740,7 +6728,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6784,7 +6772,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6828,7 +6816,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6872,7 +6860,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6916,7 +6904,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6960,7 +6948,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -7004,7 +6992,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7048,7 +7036,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7136,7 +7124,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7180,7 +7168,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7224,7 +7212,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7268,7 +7256,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7312,7 +7300,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7356,7 +7344,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7400,7 +7388,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7444,7 +7432,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7488,7 +7476,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7532,7 +7520,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7576,7 +7564,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7620,7 +7608,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7664,7 +7652,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7708,7 +7696,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7752,7 +7740,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7796,7 +7784,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7840,7 +7828,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7884,7 +7872,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7928,7 +7916,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7972,7 +7960,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -8016,7 +8004,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8060,7 +8048,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8104,7 +8092,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8148,7 +8136,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8192,7 +8180,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8236,7 +8224,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8280,7 +8268,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8324,7 +8312,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8412,7 +8400,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8456,7 +8444,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8544,7 +8532,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8588,7 +8576,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8632,7 +8620,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8676,7 +8664,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8720,7 +8708,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8764,7 +8752,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8808,7 +8796,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8852,7 +8840,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8896,7 +8884,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8940,7 +8928,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8984,7 +8972,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -9028,7 +9016,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9072,7 +9060,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9116,7 +9104,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9160,7 +9148,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9204,7 +9192,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9248,7 +9236,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9292,7 +9280,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9336,7 +9324,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9380,7 +9368,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9424,7 +9412,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9468,7 +9456,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9512,7 +9500,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9556,7 +9544,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9600,7 +9588,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9688,7 +9676,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9732,7 +9720,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9776,7 +9764,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9820,7 +9808,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9864,7 +9852,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9908,7 +9896,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9952,7 +9940,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9996,7 +9984,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -10040,7 +10028,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10084,7 +10072,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10128,7 +10116,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10172,7 +10160,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10216,7 +10204,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10260,7 +10248,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10304,7 +10292,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10348,7 +10336,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10392,7 +10380,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10436,7 +10424,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10480,7 +10468,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10524,7 +10512,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10612,7 +10600,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10656,7 +10644,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10700,7 +10688,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10744,7 +10732,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10788,7 +10776,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10832,7 +10820,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10876,7 +10864,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10964,7 +10952,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -11008,7 +10996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11052,7 +11040,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11096,7 +11084,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11140,7 +11128,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11184,7 +11172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11228,7 +11216,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11272,7 +11260,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11316,7 +11304,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11360,7 +11348,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11404,7 +11392,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11448,7 +11436,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11492,7 +11480,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11536,7 +11524,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11580,7 +11568,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11624,7 +11612,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11668,7 +11656,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11712,7 +11700,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11756,7 +11744,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11800,7 +11788,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11844,7 +11832,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11888,7 +11876,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11932,7 +11920,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11976,7 +11964,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -12020,7 +12008,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12064,7 +12052,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12108,7 +12096,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12152,7 +12140,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12240,7 +12228,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12284,7 +12272,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12328,7 +12316,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12372,7 +12360,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12416,7 +12404,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12460,7 +12448,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12504,7 +12492,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12548,7 +12536,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12592,7 +12580,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12680,7 +12668,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12724,7 +12712,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12768,7 +12756,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12812,7 +12800,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12856,7 +12844,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12900,7 +12888,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12944,7 +12932,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12988,7 +12976,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -13032,7 +13020,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13076,7 +13064,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13120,7 +13108,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13164,7 +13152,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13208,7 +13196,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13252,7 +13240,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13296,7 +13284,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13340,7 +13328,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13384,7 +13372,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13428,7 +13416,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13516,7 +13504,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13560,7 +13548,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13604,7 +13592,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13648,7 +13636,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13692,7 +13680,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13736,7 +13724,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13780,7 +13768,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13824,7 +13812,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13868,7 +13856,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13912,7 +13900,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13956,7 +13944,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -14000,7 +13988,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -14044,7 +14032,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14088,7 +14076,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14132,7 +14120,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14176,7 +14164,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14220,7 +14208,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14264,7 +14252,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14308,7 +14296,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14352,7 +14340,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14396,7 +14384,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14440,7 +14428,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14484,7 +14472,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14528,7 +14516,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14572,7 +14560,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14616,7 +14604,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14660,7 +14648,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14792,7 +14780,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14836,7 +14824,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14880,7 +14868,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14924,7 +14912,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14968,7 +14956,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -15012,7 +15000,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15056,7 +15044,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15100,7 +15088,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15144,7 +15132,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15188,7 +15176,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15232,7 +15220,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15276,7 +15264,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15320,7 +15308,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15364,7 +15352,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15408,7 +15396,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15452,7 +15440,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15496,7 +15484,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15540,7 +15528,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15584,7 +15572,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15628,7 +15616,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15672,7 +15660,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15716,7 +15704,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15760,7 +15748,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15804,7 +15792,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15848,7 +15836,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15892,7 +15880,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15936,7 +15924,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15980,7 +15968,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16068,7 +16056,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16112,7 +16100,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16156,7 +16144,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16200,7 +16188,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16244,7 +16232,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16288,7 +16276,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16332,7 +16320,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -16376,7 +16364,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -16434,79 +16422,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16524,7 +16512,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16542,7 +16530,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16560,7 +16548,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16578,7 +16566,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16596,7 +16584,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16614,7 +16602,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16632,7 +16620,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16650,7 +16638,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16668,7 +16656,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16686,7 +16674,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16704,7 +16692,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16722,7 +16710,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16766,7 +16754,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16810,7 +16798,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16854,7 +16842,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16898,7 +16886,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16942,7 +16930,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16986,7 +16974,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -17030,7 +17018,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -17074,7 +17062,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -17118,7 +17106,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17162,7 +17150,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17206,7 +17194,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17250,7 +17238,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17294,7 +17282,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17338,7 +17326,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17382,7 +17370,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17426,7 +17414,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17470,7 +17458,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17514,7 +17502,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17558,7 +17546,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17602,7 +17590,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17646,7 +17634,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17690,7 +17678,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17734,7 +17722,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17778,7 +17766,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17866,7 +17854,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17910,7 +17898,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17954,7 +17942,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17998,7 +17986,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -18042,7 +18030,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -18086,7 +18074,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -18130,7 +18118,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18174,7 +18162,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18218,7 +18206,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18262,7 +18250,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18306,7 +18294,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18350,7 +18338,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18394,7 +18382,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18438,7 +18426,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18482,7 +18470,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18526,7 +18514,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18570,7 +18558,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18614,7 +18602,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18658,7 +18646,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18702,7 +18690,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18746,7 +18734,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18790,7 +18778,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18834,7 +18822,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18878,7 +18866,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18922,7 +18910,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18966,7 +18954,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -19010,7 +18998,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -19054,7 +19042,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -19098,7 +19086,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19142,7 +19130,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19186,7 +19174,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19230,7 +19218,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19274,7 +19262,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19318,7 +19306,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19362,7 +19350,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19406,7 +19394,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19450,7 +19438,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19494,7 +19482,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19538,7 +19526,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19582,7 +19570,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19626,7 +19614,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19670,7 +19658,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19714,7 +19702,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19758,7 +19746,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19802,7 +19790,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19846,7 +19834,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19890,7 +19878,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19934,7 +19922,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19978,7 +19966,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -20022,7 +20010,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -20066,7 +20054,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -20110,7 +20098,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20154,7 +20142,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20198,7 +20186,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20242,7 +20230,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20286,7 +20274,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20330,7 +20318,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20374,7 +20362,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20418,7 +20406,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20462,7 +20450,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20506,7 +20494,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20550,7 +20538,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20594,7 +20582,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20638,7 +20626,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20682,7 +20670,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20726,7 +20714,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20770,7 +20758,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20814,7 +20802,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20858,7 +20846,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20902,7 +20890,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20946,7 +20934,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20990,7 +20978,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -21034,7 +21022,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -21078,7 +21066,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -21122,7 +21110,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21166,7 +21154,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21210,7 +21198,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21254,7 +21242,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21298,7 +21286,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21342,7 +21330,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21386,7 +21374,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21430,7 +21418,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21474,7 +21462,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21518,7 +21506,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21562,7 +21550,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21606,7 +21594,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21650,7 +21638,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21694,7 +21682,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21738,7 +21726,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21782,7 +21770,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21826,7 +21814,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21870,7 +21858,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21914,7 +21902,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21958,7 +21946,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -22002,7 +21990,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -22046,7 +22034,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -22090,7 +22078,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22134,7 +22122,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22178,7 +22166,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22222,7 +22210,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22266,7 +22254,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22310,7 +22298,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22354,7 +22342,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22398,7 +22386,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22442,7 +22430,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22486,7 +22474,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22530,7 +22518,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22574,7 +22562,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22618,7 +22606,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22662,7 +22650,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22706,7 +22694,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22750,7 +22738,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22794,7 +22782,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22838,7 +22826,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22882,7 +22870,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22926,7 +22914,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22970,7 +22958,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -23014,7 +23002,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -23058,7 +23046,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -23102,7 +23090,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23146,7 +23134,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23190,7 +23178,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23234,7 +23222,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23278,7 +23266,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23322,7 +23310,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23366,7 +23354,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23410,7 +23398,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23454,7 +23442,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23498,7 +23486,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23542,7 +23530,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23586,7 +23574,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23630,7 +23618,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23674,7 +23662,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23718,7 +23706,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23762,7 +23750,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23806,7 +23794,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23850,7 +23838,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23894,7 +23882,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23938,7 +23926,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23982,7 +23970,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -24026,7 +24014,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -24070,7 +24058,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -24114,7 +24102,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24158,7 +24146,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24202,7 +24190,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24246,7 +24234,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24290,7 +24278,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24334,7 +24322,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24378,7 +24366,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24422,7 +24410,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24466,7 +24454,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24510,7 +24498,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24554,7 +24542,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24598,7 +24586,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24642,7 +24630,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24686,7 +24674,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24730,7 +24718,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24774,7 +24762,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24818,7 +24806,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24862,7 +24850,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24906,7 +24894,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24950,7 +24938,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24994,7 +24982,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -25038,7 +25026,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -25082,7 +25070,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -25126,7 +25114,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25170,7 +25158,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25214,7 +25202,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25258,7 +25246,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25302,7 +25290,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25346,7 +25334,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25390,7 +25378,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25434,7 +25422,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25478,7 +25466,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25522,7 +25510,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25566,7 +25554,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25610,7 +25598,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25654,7 +25642,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25698,7 +25686,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25742,7 +25730,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25786,7 +25774,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25830,7 +25818,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25874,7 +25862,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25918,7 +25906,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25962,7 +25950,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -26006,7 +25994,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -26050,7 +26038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -26094,7 +26082,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26138,7 +26126,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26182,7 +26170,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26226,7 +26214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26270,7 +26258,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26314,7 +26302,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26358,7 +26346,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26402,7 +26390,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26446,7 +26434,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26490,7 +26478,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26534,7 +26522,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26578,7 +26566,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26622,7 +26610,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26666,7 +26654,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26710,7 +26698,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26754,7 +26742,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26798,7 +26786,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26842,7 +26830,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26886,7 +26874,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26930,7 +26918,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26974,7 +26962,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -27018,7 +27006,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -27062,7 +27050,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -27106,7 +27094,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27150,7 +27138,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27194,7 +27182,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27238,7 +27226,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27282,7 +27270,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27326,7 +27314,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27370,7 +27358,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27414,7 +27402,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27458,7 +27446,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27502,7 +27490,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27546,7 +27534,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27590,7 +27578,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -27634,7 +27622,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -27692,32 +27680,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -455,7 +455,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>3.59652332</v>
+        <v>3.6</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -466,10 +466,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>3.59738699</v>
+        <v>3.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02401402474432324</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -479,10 +479,10 @@
         <v>38412</v>
       </c>
       <c r="B4" t="n">
-        <v>3.60671488</v>
+        <v>3.61</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2592962621461137</v>
+        <v>0.2777777777777768</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -492,10 +492,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>3.63247488</v>
+        <v>3.63</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7142233544116472</v>
+        <v>0.5540166204986097</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -505,10 +505,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>3.6657744</v>
+        <v>3.67</v>
       </c>
       <c r="C6" t="n">
-        <v>0.916717144648227</v>
+        <v>1.101928374655659</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -518,10 +518,10 @@
         <v>38504</v>
       </c>
       <c r="B7" t="n">
-        <v>3.66954416</v>
+        <v>3.67</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1028366611977027</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,10 +531,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>3.64849635</v>
+        <v>3.65</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5735810520944962</v>
+        <v>-0.544959128065392</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -544,10 +544,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>3.67959685</v>
+        <v>3.68</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8524196550176111</v>
+        <v>0.8219178082191858</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -557,10 +557,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>3.71729441</v>
+        <v>3.72</v>
       </c>
       <c r="C10" t="n">
-        <v>1.024502453305454</v>
+        <v>1.086956521739135</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -570,10 +570,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>3.78389345</v>
+        <v>3.78</v>
       </c>
       <c r="C11" t="n">
-        <v>1.791599821118273</v>
+        <v>1.61290322580645</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -583,10 +583,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>3.83698419</v>
+        <v>3.84</v>
       </c>
       <c r="C12" t="n">
-        <v>1.403071748756557</v>
+        <v>1.587301587301582</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -596,10 +596,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>3.85300566</v>
+        <v>3.85</v>
       </c>
       <c r="C13" t="n">
-        <v>0.417553714236174</v>
+        <v>0.2604166666666741</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -609,16 +609,16 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>3.88190713</v>
+        <v>3.88</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7501019347062154</v>
+        <v>0.7792207792207684</v>
       </c>
       <c r="D14" t="n">
-        <v>7.93499122925192</v>
+        <v>7.777777777777772</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7501019347062154</v>
+        <v>0.7792207792207684</v>
       </c>
     </row>
     <row r="15">
@@ -626,16 +626,16 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>3.89038908</v>
+        <v>3.89</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2184995600345463</v>
+        <v>0.2577319587628857</v>
       </c>
       <c r="D15" t="n">
-        <v>8.144858777064744</v>
+        <v>8.05555555555555</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9702404641679152</v>
+        <v>1.038961038961039</v>
       </c>
     </row>
     <row r="16">
@@ -643,16 +643,16 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>3.90107006</v>
+        <v>3.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2745478609044394</v>
+        <v>0.2570694087403513</v>
       </c>
       <c r="D16" t="n">
-        <v>8.161309939753259</v>
+        <v>8.033240997229928</v>
       </c>
       <c r="E16" t="n">
-        <v>1.247452099512358</v>
+        <v>1.298701298701288</v>
       </c>
     </row>
     <row r="17">
@@ -660,16 +660,16 @@
         <v>38808</v>
       </c>
       <c r="B17" t="n">
-        <v>3.95321836</v>
+        <v>3.95</v>
       </c>
       <c r="C17" t="n">
-        <v>1.33676912226488</v>
+        <v>1.2820512820513</v>
       </c>
       <c r="D17" t="n">
-        <v>8.82988845335111</v>
+        <v>8.815426997245179</v>
       </c>
       <c r="E17" t="n">
-        <v>2.600896776258566</v>
+        <v>2.597402597402598</v>
       </c>
     </row>
     <row r="18">
@@ -677,16 +677,16 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>4.02735692</v>
+        <v>4.03</v>
       </c>
       <c r="C18" t="n">
-        <v>1.87539754318049</v>
+        <v>2.025316455696213</v>
       </c>
       <c r="D18" t="n">
-        <v>9.863741751265431</v>
+        <v>9.809264305177123</v>
       </c>
       <c r="E18" t="n">
-        <v>4.525071473681663</v>
+        <v>4.675324675324677</v>
       </c>
     </row>
     <row r="19">
@@ -694,16 +694,16 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>4.04086521</v>
+        <v>4.04</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3354132814232802</v>
+        <v>0.2481389578163684</v>
       </c>
       <c r="D19" t="n">
-        <v>10.11899663308589</v>
+        <v>10.08174386920981</v>
       </c>
       <c r="E19" t="n">
-        <v>4.875662445821582</v>
+        <v>4.935064935064926</v>
       </c>
     </row>
     <row r="20">
@@ -711,16 +711,16 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>4.07510717</v>
+        <v>4.08</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8473917891460792</v>
+        <v>0.990099009900991</v>
       </c>
       <c r="D20" t="n">
-        <v>11.6927846179701</v>
+        <v>11.78082191780823</v>
       </c>
       <c r="E20" t="n">
-        <v>5.76437019820002</v>
+        <v>5.974025974025965</v>
       </c>
     </row>
     <row r="21">
@@ -728,16 +728,16 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>4.05720082</v>
+        <v>4.06</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.4394080757390117</v>
+        <v>-0.4901960784313819</v>
       </c>
       <c r="D21" t="n">
-        <v>10.26210167562245</v>
+        <v>10.32608695652173</v>
       </c>
       <c r="E21" t="n">
-        <v>5.299633014294614</v>
+        <v>5.454545454545445</v>
       </c>
     </row>
     <row r="22">
@@ -745,16 +745,16 @@
         <v>38961</v>
       </c>
       <c r="B22" t="n">
-        <v>4.10934913</v>
+        <v>4.11</v>
       </c>
       <c r="C22" t="n">
-        <v>1.285327306031636</v>
+        <v>1.231527093596085</v>
       </c>
       <c r="D22" t="n">
-        <v>10.54677614302817</v>
+        <v>10.48387096774195</v>
       </c>
       <c r="E22" t="n">
-        <v>6.653077950578457</v>
+        <v>6.753246753246755</v>
       </c>
     </row>
     <row r="23">
@@ -762,16 +762,16 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>4.16149743</v>
+        <v>4.16</v>
       </c>
       <c r="C23" t="n">
-        <v>1.269016049750915</v>
+        <v>1.216545012165438</v>
       </c>
       <c r="D23" t="n">
-        <v>9.979244526560338</v>
+        <v>10.05291005291007</v>
       </c>
       <c r="E23" t="n">
-        <v>8.006522627324664</v>
+        <v>8.051948051948044</v>
       </c>
     </row>
     <row r="24">
@@ -779,16 +779,16 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>4.21521647</v>
+        <v>4.22</v>
       </c>
       <c r="C24" t="n">
-        <v>1.290858420643071</v>
+        <v>1.442307692307687</v>
       </c>
       <c r="D24" t="n">
-        <v>9.857540747385762</v>
+        <v>9.895833333333325</v>
       </c>
       <c r="E24" t="n">
-        <v>9.400733919503246</v>
+        <v>9.610389610389603</v>
       </c>
     </row>
     <row r="25">
@@ -796,16 +796,16 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>4.22495501</v>
+        <v>4.22</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2310329746837647</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>9.65348568940334</v>
+        <v>9.610389610389603</v>
       </c>
       <c r="E25" t="n">
-        <v>9.65348568940334</v>
+        <v>9.610389610389603</v>
       </c>
     </row>
     <row r="26">
@@ -813,16 +813,16 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>4.26736477</v>
+        <v>4.27</v>
       </c>
       <c r="C26" t="n">
-        <v>1.003791990674952</v>
+        <v>1.184834123222744</v>
       </c>
       <c r="D26" t="n">
-        <v>9.929594580486523</v>
+        <v>10.05154639175256</v>
       </c>
       <c r="E26" t="n">
-        <v>1.003791990674952</v>
+        <v>1.184834123222744</v>
       </c>
     </row>
     <row r="27">
@@ -830,16 +830,16 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>4.28558526</v>
+        <v>4.29</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4269728739406453</v>
+        <v>0.4683840749414525</v>
       </c>
       <c r="D27" t="n">
-        <v>10.15826879711477</v>
+        <v>10.28277634961439</v>
       </c>
       <c r="E27" t="n">
-        <v>1.435050784126579</v>
+        <v>1.65876777251186</v>
       </c>
     </row>
     <row r="28">
@@ -847,16 +847,16 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>4.32485356</v>
+        <v>4.32</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9162879190974138</v>
+        <v>0.6993006993007089</v>
       </c>
       <c r="D28" t="n">
-        <v>10.86326298892464</v>
+        <v>10.76923076923078</v>
       </c>
       <c r="E28" t="n">
-        <v>2.364487900191858</v>
+        <v>2.369668246445511</v>
       </c>
     </row>
     <row r="29">
@@ -864,16 +864,16 @@
         <v>39173</v>
       </c>
       <c r="B29" t="n">
-        <v>4.37700187</v>
+        <v>4.38</v>
       </c>
       <c r="C29" t="n">
-        <v>1.205782098203567</v>
+        <v>1.388888888888884</v>
       </c>
       <c r="D29" t="n">
-        <v>10.71996210196695</v>
+        <v>10.88607594936708</v>
       </c>
       <c r="E29" t="n">
-        <v>3.598780570210125</v>
+        <v>3.791469194312791</v>
       </c>
     </row>
     <row r="30">
@@ -881,16 +881,16 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>4.39899211</v>
+        <v>4.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5024041719223771</v>
+        <v>0.4566210045662267</v>
       </c>
       <c r="D30" t="n">
-        <v>9.227768915996659</v>
+        <v>9.181141439205964</v>
       </c>
       <c r="E30" t="n">
-        <v>4.119265165855568</v>
+        <v>4.265402843601906</v>
       </c>
     </row>
     <row r="31">
@@ -898,16 +898,16 @@
         <v>39234</v>
       </c>
       <c r="B31" t="n">
-        <v>4.38831114</v>
+        <v>4.39</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2428049365153395</v>
+        <v>-0.2272727272727426</v>
       </c>
       <c r="D31" t="n">
-        <v>8.598305361440151</v>
+        <v>8.663366336633649</v>
       </c>
       <c r="E31" t="n">
-        <v>3.866458450169374</v>
+        <v>4.028436018957349</v>
       </c>
     </row>
     <row r="32">
@@ -915,16 +915,16 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>4.3562682</v>
+        <v>4.36</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.730188425062317</v>
+        <v>-0.6833712984054552</v>
       </c>
       <c r="D32" t="n">
-        <v>6.899475725935322</v>
+        <v>6.862745098039214</v>
       </c>
       <c r="E32" t="n">
-        <v>3.108037593044077</v>
+        <v>3.31753554502372</v>
       </c>
     </row>
     <row r="33">
@@ -932,16 +932,16 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>4.35721064</v>
+        <v>4.36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02163411334499266</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>7.394502596989994</v>
+        <v>7.389162561576379</v>
       </c>
       <c r="E33" t="n">
-        <v>3.130344102764759</v>
+        <v>3.31753554502372</v>
       </c>
     </row>
     <row r="34">
@@ -949,16 +949,16 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>4.40213358</v>
+        <v>4.4</v>
       </c>
       <c r="C34" t="n">
-        <v>1.031002256067204</v>
+        <v>0.917431192660545</v>
       </c>
       <c r="D34" t="n">
-        <v>7.124837553045782</v>
+        <v>7.055961070559613</v>
       </c>
       <c r="E34" t="n">
-        <v>4.193620277154131</v>
+        <v>4.265402843601906</v>
       </c>
     </row>
     <row r="35">
@@ -966,16 +966,16 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>4.48192676</v>
+        <v>4.48</v>
       </c>
       <c r="C35" t="n">
-        <v>1.812602424481646</v>
+        <v>1.81818181818183</v>
       </c>
       <c r="D35" t="n">
-        <v>7.699856491320745</v>
+        <v>7.692307692307709</v>
       </c>
       <c r="E35" t="n">
-        <v>6.08223636445302</v>
+        <v>6.161137440758302</v>
       </c>
     </row>
     <row r="36">
@@ -983,16 +983,16 @@
         <v>39387</v>
       </c>
       <c r="B36" t="n">
-        <v>4.56925947</v>
+        <v>4.57</v>
       </c>
       <c r="C36" t="n">
-        <v>1.948552813924165</v>
+        <v>2.008928571428559</v>
       </c>
       <c r="D36" t="n">
-        <v>8.399165322107427</v>
+        <v>8.293838862559255</v>
       </c>
       <c r="E36" t="n">
-        <v>8.149304766206257</v>
+        <v>8.293838862559255</v>
       </c>
     </row>
     <row r="37">
@@ -1000,16 +1000,16 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>4.57931215</v>
+        <v>4.58</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2200067662167404</v>
+        <v>0.2188183807439792</v>
       </c>
       <c r="D37" t="n">
-        <v>8.387240554308285</v>
+        <v>8.530805687203792</v>
       </c>
       <c r="E37" t="n">
-        <v>8.387240554308285</v>
+        <v>8.530805687203792</v>
       </c>
     </row>
     <row r="38">
@@ -1017,16 +1017,16 @@
         <v>39448</v>
       </c>
       <c r="B38" t="n">
-        <v>4.61606728</v>
+        <v>4.62</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8026342995639757</v>
+        <v>0.8733624454148492</v>
       </c>
       <c r="D38" t="n">
-        <v>8.171378093839387</v>
+        <v>8.196721311475418</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8026342995639757</v>
+        <v>0.8733624454148492</v>
       </c>
     </row>
     <row r="39">
@@ -1034,16 +1034,16 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>4.6757551</v>
+        <v>4.68</v>
       </c>
       <c r="C39" t="n">
-        <v>1.293044844874958</v>
+        <v>1.298701298701288</v>
       </c>
       <c r="D39" t="n">
-        <v>9.104237025493212</v>
+        <v>9.090909090909083</v>
       </c>
       <c r="E39" t="n">
-        <v>2.106057565872632</v>
+        <v>2.183406113537112</v>
       </c>
     </row>
     <row r="40">
@@ -1051,16 +1051,16 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>4.72067803</v>
+        <v>4.72</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9607631075460032</v>
+        <v>0.8547008547008517</v>
       </c>
       <c r="D40" t="n">
-        <v>9.152320755110143</v>
+        <v>9.259259259259256</v>
       </c>
       <c r="E40" t="n">
-        <v>3.087054897535224</v>
+        <v>3.056768558951961</v>
       </c>
     </row>
     <row r="41">
@@ -1068,16 +1068,16 @@
         <v>39539</v>
       </c>
       <c r="B41" t="n">
-        <v>4.79984293</v>
+        <v>4.8</v>
       </c>
       <c r="C41" t="n">
-        <v>1.676981558515633</v>
+        <v>1.694915254237284</v>
       </c>
       <c r="D41" t="n">
-        <v>9.660518148236473</v>
+        <v>9.589041095890405</v>
       </c>
       <c r="E41" t="n">
-        <v>4.815805797383788</v>
+        <v>4.803493449781659</v>
       </c>
     </row>
     <row r="42">
@@ -1085,16 +1085,16 @@
         <v>39569</v>
       </c>
       <c r="B42" t="n">
-        <v>4.87146831</v>
+        <v>4.87</v>
       </c>
       <c r="C42" t="n">
-        <v>1.492244247250829</v>
+        <v>1.458333333333339</v>
       </c>
       <c r="D42" t="n">
-        <v>10.7405557497124</v>
+        <v>10.68181818181817</v>
       </c>
       <c r="E42" t="n">
-        <v>6.379913629604839</v>
+        <v>6.331877729257651</v>
       </c>
     </row>
     <row r="43">
@@ -1102,16 +1102,16 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>4.85387611</v>
+        <v>4.85</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3611272593909254</v>
+        <v>-0.4106776180698213</v>
       </c>
       <c r="D43" t="n">
-        <v>10.60920602817603</v>
+        <v>10.47835990888382</v>
       </c>
       <c r="E43" t="n">
-        <v>5.99574676297181</v>
+        <v>5.895196506550215</v>
       </c>
     </row>
     <row r="44">
@@ -1119,16 +1119,16 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>4.88183514</v>
+        <v>4.88</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5760144957634772</v>
+        <v>0.6185567010309256</v>
       </c>
       <c r="D44" t="n">
-        <v>12.06461392804052</v>
+        <v>11.92660550458715</v>
       </c>
       <c r="E44" t="n">
-        <v>6.606297629219271</v>
+        <v>6.550218340611358</v>
       </c>
     </row>
     <row r="45">
@@ -1136,16 +1136,16 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>4.86989758</v>
+        <v>4.87</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2445301747735718</v>
+        <v>-0.2049180327868827</v>
       </c>
       <c r="D45" t="n">
-        <v>11.76640246155278</v>
+        <v>11.69724770642202</v>
       </c>
       <c r="E45" t="n">
-        <v>6.345613063306899</v>
+        <v>6.331877729257651</v>
       </c>
     </row>
     <row r="46">
@@ -1153,16 +1153,16 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>4.89188782</v>
+        <v>4.89</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4515544657512027</v>
+        <v>0.4106776180698102</v>
       </c>
       <c r="D46" t="n">
-        <v>11.12538343282168</v>
+        <v>11.13636363636361</v>
       </c>
       <c r="E46" t="n">
-        <v>6.825821428224765</v>
+        <v>6.768558951965065</v>
       </c>
     </row>
     <row r="47">
@@ -1170,16 +1170,16 @@
         <v>39722</v>
       </c>
       <c r="B47" t="n">
-        <v>5.01911712</v>
+        <v>5.02</v>
       </c>
       <c r="C47" t="n">
-        <v>2.600822109612477</v>
+        <v>2.658486707566454</v>
       </c>
       <c r="D47" t="n">
-        <v>11.98570143524611</v>
+        <v>12.05357142857142</v>
       </c>
       <c r="E47" t="n">
-        <v>9.604171010705187</v>
+        <v>9.606986899563296</v>
       </c>
     </row>
     <row r="48">
@@ -1187,16 +1187,16 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>5.06089859</v>
+        <v>5.06</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8324466036767841</v>
+        <v>0.7968127490039834</v>
       </c>
       <c r="D48" t="n">
-        <v>10.75971113542387</v>
+        <v>10.72210065645514</v>
       </c>
       <c r="E48" t="n">
-        <v>10.5165672097719</v>
+        <v>10.48034934497815</v>
       </c>
     </row>
     <row r="49">
@@ -1204,16 +1204,16 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>5.04016493</v>
+        <v>5.04</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4096833720590221</v>
+        <v>-0.395256916996034</v>
       </c>
       <c r="D49" t="n">
-        <v>10.06379921054301</v>
+        <v>10.04366812227073</v>
       </c>
       <c r="E49" t="n">
-        <v>10.06379921054301</v>
+        <v>10.04366812227073</v>
       </c>
     </row>
     <row r="50">
@@ -1221,16 +1221,16 @@
         <v>39814</v>
       </c>
       <c r="B50" t="n">
-        <v>5.05461566</v>
+        <v>5.05</v>
       </c>
       <c r="C50" t="n">
-        <v>0.286711450928645</v>
+        <v>0.1984126984126977</v>
       </c>
       <c r="D50" t="n">
-        <v>9.50047634487683</v>
+        <v>9.307359307359309</v>
       </c>
       <c r="E50" t="n">
-        <v>0.286711450928645</v>
+        <v>0.1984126984126977</v>
       </c>
     </row>
     <row r="51">
@@ -1238,16 +1238,16 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>5.03733761</v>
+        <v>5.04</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.3418271766284953</v>
+        <v>-0.1980198019801982</v>
       </c>
       <c r="D51" t="n">
-        <v>7.733136194408474</v>
+        <v>7.692307692307709</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.05609578335764587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1255,16 +1255,16 @@
         <v>39873</v>
       </c>
       <c r="B52" t="n">
-        <v>5.09294152</v>
+        <v>5.09</v>
       </c>
       <c r="C52" t="n">
-        <v>1.103835285719512</v>
+        <v>0.9920634920634885</v>
       </c>
       <c r="D52" t="n">
-        <v>7.885805548149194</v>
+        <v>7.83898305084747</v>
       </c>
       <c r="E52" t="n">
-        <v>1.047120297311377</v>
+        <v>0.9920634920634885</v>
       </c>
     </row>
     <row r="53">
@@ -1272,16 +1272,16 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>5.09388396</v>
+        <v>5.09</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01850482665664011</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>6.126055254062246</v>
+        <v>6.041666666666679</v>
       </c>
       <c r="E53" t="n">
-        <v>1.065818891763914</v>
+        <v>0.9920634920634885</v>
       </c>
     </row>
     <row r="54">
@@ -1289,16 +1289,16 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>5.12655519</v>
+        <v>5.13</v>
       </c>
       <c r="C54" t="n">
-        <v>0.6413815127425782</v>
+        <v>0.7858546168958647</v>
       </c>
       <c r="D54" t="n">
-        <v>5.236344850614461</v>
+        <v>5.338809034907599</v>
       </c>
       <c r="E54" t="n">
-        <v>1.714036369837602</v>
+        <v>1.785714285714279</v>
       </c>
     </row>
     <row r="55">
@@ -1306,16 +1306,16 @@
         <v>39965</v>
       </c>
       <c r="B55" t="n">
-        <v>5.13220982</v>
+        <v>5.13</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1103007729445604</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>5.734256575411445</v>
+        <v>5.773195876288661</v>
       </c>
       <c r="E55" t="n">
-        <v>1.826227738146646</v>
+        <v>1.785714285714279</v>
       </c>
     </row>
     <row r="56">
@@ -1323,16 +1323,16 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>5.14508983</v>
+        <v>5.15</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2509642133064593</v>
+        <v>0.3898635477582957</v>
       </c>
       <c r="D56" t="n">
-        <v>5.392535439039836</v>
+        <v>5.532786885245922</v>
       </c>
       <c r="E56" t="n">
-        <v>2.08177512952934</v>
+        <v>2.182539682539697</v>
       </c>
     </row>
     <row r="57">
@@ -1340,16 +1340,16 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>5.12969665</v>
+        <v>5.13</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2991819483937008</v>
+        <v>-0.3883495145631133</v>
       </c>
       <c r="D57" t="n">
-        <v>5.334795357236244</v>
+        <v>5.338809034907599</v>
       </c>
       <c r="E57" t="n">
-        <v>1.776364885741932</v>
+        <v>1.785714285714279</v>
       </c>
     </row>
     <row r="58">
@@ -1357,16 +1357,16 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>5.14980202</v>
+        <v>5.15</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3919407203153202</v>
+        <v>0.3898635477582957</v>
       </c>
       <c r="D58" t="n">
-        <v>5.272283615040063</v>
+        <v>5.316973415132931</v>
       </c>
       <c r="E58" t="n">
-        <v>2.175267903385847</v>
+        <v>2.182539682539697</v>
       </c>
     </row>
     <row r="59">
@@ -1374,16 +1374,16 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>5.27388985</v>
+        <v>5.27</v>
       </c>
       <c r="C59" t="n">
-        <v>2.409565057415541</v>
+        <v>2.330097087378635</v>
       </c>
       <c r="D59" t="n">
-        <v>5.076046721141259</v>
+        <v>4.980079681274896</v>
       </c>
       <c r="E59" t="n">
-        <v>4.637247456106541</v>
+        <v>4.563492063492047</v>
       </c>
     </row>
     <row r="60">
@@ -1391,16 +1391,16 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>5.34080304</v>
+        <v>5.34</v>
       </c>
       <c r="C60" t="n">
-        <v>1.268763510485527</v>
+        <v>1.328273244781797</v>
       </c>
       <c r="D60" t="n">
-        <v>5.530726313170398</v>
+        <v>5.533596837944676</v>
       </c>
       <c r="E60" t="n">
-        <v>5.96484667020607</v>
+        <v>5.952380952380953</v>
       </c>
     </row>
     <row r="61">
@@ -1408,16 +1408,16 @@
         <v>40148</v>
       </c>
       <c r="B61" t="n">
-        <v>5.36907621</v>
+        <v>5.37</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5293805030488485</v>
+        <v>0.5617977528090012</v>
       </c>
       <c r="D61" t="n">
-        <v>6.525803908563765</v>
+        <v>6.547619047619047</v>
       </c>
       <c r="E61" t="n">
-        <v>6.525803908563765</v>
+        <v>6.547619047619047</v>
       </c>
     </row>
     <row r="62">
@@ -1425,16 +1425,16 @@
         <v>40179</v>
       </c>
       <c r="B62" t="n">
-        <v>5.46834648</v>
+        <v>5.47</v>
       </c>
       <c r="C62" t="n">
-        <v>1.848926446883126</v>
+        <v>1.862197392923637</v>
       </c>
       <c r="D62" t="n">
-        <v>8.185208289407321</v>
+        <v>8.316831683168324</v>
       </c>
       <c r="E62" t="n">
-        <v>1.848926446883126</v>
+        <v>1.862197392923637</v>
       </c>
     </row>
     <row r="63">
@@ -1442,16 +1442,16 @@
         <v>40210</v>
       </c>
       <c r="B63" t="n">
-        <v>5.54751137</v>
+        <v>5.55</v>
       </c>
       <c r="C63" t="n">
-        <v>1.447693380248283</v>
+        <v>1.462522851919568</v>
       </c>
       <c r="D63" t="n">
-        <v>10.12784529246591</v>
+        <v>10.11904761904761</v>
       </c>
       <c r="E63" t="n">
-        <v>3.323386612908585</v>
+        <v>3.351955307262555</v>
       </c>
     </row>
     <row r="64">
@@ -1459,16 +1459,16 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>5.57986845</v>
+        <v>5.58</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5832719906620154</v>
+        <v>0.540540540540535</v>
       </c>
       <c r="D64" t="n">
-        <v>9.560819186472802</v>
+        <v>9.626719056974453</v>
       </c>
       <c r="E64" t="n">
-        <v>3.926042986825107</v>
+        <v>3.910614525139655</v>
       </c>
     </row>
     <row r="65">
@@ -1476,16 +1476,16 @@
         <v>40269</v>
       </c>
       <c r="B65" t="n">
-        <v>5.61316797</v>
+        <v>5.61</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5967796606387799</v>
+        <v>0.5376344086021501</v>
       </c>
       <c r="D65" t="n">
-        <v>10.19426461375457</v>
+        <v>10.21611001964637</v>
       </c>
       <c r="E65" t="n">
-        <v>4.546252473477175</v>
+        <v>4.469273743016755</v>
       </c>
     </row>
     <row r="66">
@@ -1493,16 +1493,16 @@
         <v>40299</v>
       </c>
       <c r="B66" t="n">
-        <v>5.5930626</v>
+        <v>5.59</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3581822262838985</v>
+        <v>-0.3565062388591889</v>
       </c>
       <c r="D66" t="n">
-        <v>9.099822253157086</v>
+        <v>8.966861598440534</v>
       </c>
       <c r="E66" t="n">
-        <v>4.171786378871301</v>
+        <v>4.096834264432014</v>
       </c>
     </row>
     <row r="67">
@@ -1510,16 +1510,16 @@
         <v>40330</v>
       </c>
       <c r="B67" t="n">
-        <v>5.56164796</v>
+        <v>5.56</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5616715250067017</v>
+        <v>-0.536672629695889</v>
       </c>
       <c r="D67" t="n">
-        <v>8.367509417220198</v>
+        <v>8.382066276803112</v>
       </c>
       <c r="E67" t="n">
-        <v>3.58668311769037</v>
+        <v>3.538175046554914</v>
       </c>
     </row>
     <row r="68">
@@ -1527,16 +1527,16 @@
         <v>40360</v>
       </c>
       <c r="B68" t="n">
-        <v>5.53494552</v>
+        <v>5.53</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.480117407503089</v>
+        <v>-0.5395683453237266</v>
       </c>
       <c r="D68" t="n">
-        <v>7.577237771959378</v>
+        <v>7.37864077669903</v>
       </c>
       <c r="E68" t="n">
-        <v>3.089345420187284</v>
+        <v>2.979515828677837</v>
       </c>
     </row>
     <row r="69">
@@ -1544,16 +1544,16 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>5.55724991</v>
+        <v>5.56</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4029739754330963</v>
+        <v>0.5424954792043302</v>
       </c>
       <c r="D69" t="n">
-        <v>8.334864401777065</v>
+        <v>8.382066276803112</v>
       </c>
       <c r="E69" t="n">
-        <v>3.504768653674972</v>
+        <v>3.538175046554914</v>
       </c>
     </row>
     <row r="70">
@@ -1561,16 +1561,16 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>5.62541968</v>
+        <v>5.63</v>
       </c>
       <c r="C70" t="n">
-        <v>1.22668174194096</v>
+        <v>1.25899280575541</v>
       </c>
       <c r="D70" t="n">
-        <v>9.235649412402068</v>
+        <v>9.320388349514563</v>
       </c>
       <c r="E70" t="n">
-        <v>4.774442752787822</v>
+        <v>4.841713221601496</v>
       </c>
     </row>
     <row r="71">
@@ -1578,16 +1578,16 @@
         <v>40452</v>
       </c>
       <c r="B71" t="n">
-        <v>5.7284597</v>
+        <v>5.73</v>
       </c>
       <c r="C71" t="n">
-        <v>1.831685916098613</v>
+        <v>1.776198934280648</v>
       </c>
       <c r="D71" t="n">
-        <v>8.61925187914192</v>
+        <v>8.72865275142316</v>
       </c>
       <c r="E71" t="n">
-        <v>6.693581464361453</v>
+        <v>6.703910614525155</v>
       </c>
     </row>
     <row r="72">
@@ -1595,16 +1595,16 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>5.73003043</v>
+        <v>5.73</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0274197617205818</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>7.287806479379189</v>
+        <v>7.303370786516861</v>
       </c>
       <c r="E72" t="n">
-        <v>6.722836590170145</v>
+        <v>6.703910614525155</v>
       </c>
     </row>
     <row r="73">
@@ -1612,16 +1612,16 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>5.71275238</v>
+        <v>5.71</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3015350478688394</v>
+        <v>-0.3490401396160636</v>
       </c>
       <c r="D73" t="n">
-        <v>6.401029833770977</v>
+        <v>6.331471135940414</v>
       </c>
       <c r="E73" t="n">
-        <v>6.401029833770977</v>
+        <v>6.331471135940414</v>
       </c>
     </row>
     <row r="74">
@@ -1629,16 +1629,16 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>5.73631336</v>
+        <v>5.74</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4124278181999452</v>
+        <v>0.5253940455341555</v>
       </c>
       <c r="D74" t="n">
-        <v>4.900327383790781</v>
+        <v>4.936014625228524</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4124278181999452</v>
+        <v>0.5253940455341555</v>
       </c>
     </row>
     <row r="75">
@@ -1646,16 +1646,16 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>5.77809483</v>
+        <v>5.78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7283679844156898</v>
+        <v>0.6968641114982521</v>
       </c>
       <c r="D75" t="n">
-        <v>4.156520728320734</v>
+        <v>4.144144144144146</v>
       </c>
       <c r="E75" t="n">
-        <v>1.143799794802236</v>
+        <v>1.225919439579681</v>
       </c>
     </row>
     <row r="76">
@@ -1663,16 +1663,16 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>5.80228411</v>
+        <v>5.8</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4186376428854999</v>
+        <v>0.3460207612456578</v>
       </c>
       <c r="D76" t="n">
-        <v>3.986037699508849</v>
+        <v>3.942652329749108</v>
       </c>
       <c r="E76" t="n">
-        <v>1.567225814188022</v>
+        <v>1.576182136602444</v>
       </c>
     </row>
     <row r="77">
@@ -1680,16 +1680,16 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>5.85254753</v>
+        <v>5.85</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8662695422544386</v>
+        <v>0.8620689655172376</v>
       </c>
       <c r="D77" t="n">
-        <v>4.264607103856188</v>
+        <v>4.278074866310155</v>
       </c>
       <c r="E77" t="n">
-        <v>2.447071756329122</v>
+        <v>2.451838879159363</v>
       </c>
     </row>
     <row r="78">
@@ -1697,16 +1697,16 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>5.99422756</v>
+        <v>5.99</v>
       </c>
       <c r="C78" t="n">
-        <v>2.420826644700491</v>
+        <v>2.393162393162407</v>
       </c>
       <c r="D78" t="n">
-        <v>7.172545503066607</v>
+        <v>7.155635062611809</v>
       </c>
       <c r="E78" t="n">
-        <v>4.927137766121747</v>
+        <v>4.903677758318747</v>
       </c>
     </row>
     <row r="79">
@@ -1714,16 +1714,16 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>5.90846559</v>
+        <v>5.91</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.430742646013261</v>
+        <v>-1.33555926544241</v>
       </c>
       <c r="D79" t="n">
-        <v>6.235878870693567</v>
+        <v>6.294964028776984</v>
       </c>
       <c r="E79" t="n">
-        <v>3.425900458860753</v>
+        <v>3.502626970227674</v>
       </c>
     </row>
     <row r="80">
@@ -1731,16 +1731,16 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>5.88427632</v>
+        <v>5.88</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.4094002009750186</v>
+        <v>-0.5076142131979711</v>
       </c>
       <c r="D80" t="n">
-        <v>6.311368354715063</v>
+        <v>6.329113924050622</v>
       </c>
       <c r="E80" t="n">
-        <v>3.002474614521966</v>
+        <v>2.977232924693518</v>
       </c>
     </row>
     <row r="81">
@@ -1748,16 +1748,16 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>5.92700023</v>
+        <v>5.93</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7260690640034539</v>
+        <v>0.8503401360544283</v>
       </c>
       <c r="D81" t="n">
-        <v>6.653476557436289</v>
+        <v>6.654676258992809</v>
       </c>
       <c r="E81" t="n">
-        <v>3.750343717856008</v>
+        <v>3.852889667250436</v>
       </c>
     </row>
     <row r="82">
@@ -1765,16 +1765,16 @@
         <v>40787</v>
       </c>
       <c r="B82" t="n">
-        <v>5.97160902</v>
+        <v>5.97</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7526368866025868</v>
+        <v>0.6745362563237878</v>
       </c>
       <c r="D82" t="n">
-        <v>6.154018005639705</v>
+        <v>6.039076376554164</v>
       </c>
       <c r="E82" t="n">
-        <v>4.531207074653554</v>
+        <v>4.553415061295962</v>
       </c>
     </row>
     <row r="83">
@@ -1782,16 +1782,16 @@
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>6.16700808</v>
+        <v>6.17</v>
       </c>
       <c r="C83" t="n">
-        <v>3.272134182689679</v>
+        <v>3.350083752093802</v>
       </c>
       <c r="D83" t="n">
-        <v>7.65560731796715</v>
+        <v>7.678883071553222</v>
       </c>
       <c r="E83" t="n">
-        <v>7.95160843292142</v>
+        <v>8.056042031523635</v>
       </c>
     </row>
     <row r="84">
@@ -1799,16 +1799,16 @@
         <v>40848</v>
       </c>
       <c r="B84" t="n">
-        <v>6.27350371</v>
+        <v>6.27</v>
       </c>
       <c r="C84" t="n">
-        <v>1.72686055569431</v>
+        <v>1.620745542949753</v>
       </c>
       <c r="D84" t="n">
-        <v>9.484649106828558</v>
+        <v>9.424083769633484</v>
       </c>
       <c r="E84" t="n">
-        <v>9.815782178187105</v>
+        <v>9.807355516637472</v>
       </c>
     </row>
     <row r="85">
@@ -1816,16 +1816,16 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>6.30963055</v>
+        <v>6.31</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5758638500908742</v>
+        <v>0.6379585326953707</v>
       </c>
       <c r="D85" t="n">
-        <v>10.44817156944582</v>
+        <v>10.507880910683</v>
       </c>
       <c r="E85" t="n">
-        <v>10.44817156944582</v>
+        <v>10.507880910683</v>
       </c>
     </row>
     <row r="86">
@@ -1833,16 +1833,16 @@
         <v>40909</v>
       </c>
       <c r="B86" t="n">
-        <v>6.34512909</v>
+        <v>6.35</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5626088519556927</v>
+        <v>0.6339144215530945</v>
       </c>
       <c r="D86" t="n">
-        <v>10.61336248199665</v>
+        <v>10.62717770034842</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5626088519556927</v>
+        <v>0.6339144215530945</v>
       </c>
     </row>
     <row r="87">
@@ -1850,16 +1850,16 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>6.38094178</v>
+        <v>6.38</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5644123152110492</v>
+        <v>0.4724409448819022</v>
       </c>
       <c r="D87" t="n">
-        <v>10.43331699697978</v>
+        <v>10.38062283737025</v>
       </c>
       <c r="E87" t="n">
-        <v>1.13019660081366</v>
+        <v>1.109350237717921</v>
       </c>
     </row>
     <row r="88">
@@ -1867,16 +1867,16 @@
         <v>40969</v>
       </c>
       <c r="B88" t="n">
-        <v>6.40733008</v>
+        <v>6.41</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4135486721209558</v>
+        <v>0.4702194357366851</v>
       </c>
       <c r="D88" t="n">
-        <v>10.42772050677814</v>
+        <v>10.51724137931036</v>
       </c>
       <c r="E88" t="n">
-        <v>1.548419185969618</v>
+        <v>1.584786053882725</v>
       </c>
     </row>
     <row r="89">
@@ -1884,16 +1884,16 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>6.50440132</v>
+        <v>6.5</v>
       </c>
       <c r="C89" t="n">
-        <v>1.515002954241429</v>
+        <v>1.404056162246481</v>
       </c>
       <c r="D89" t="n">
-        <v>11.13794952810918</v>
+        <v>11.11111111111112</v>
       </c>
       <c r="E89" t="n">
-        <v>3.086880736622533</v>
+        <v>3.011093502377182</v>
       </c>
     </row>
     <row r="90">
@@ -1901,16 +1901,16 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>6.49057888</v>
+        <v>6.49</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.2125090276563713</v>
+        <v>-0.1538461538461489</v>
       </c>
       <c r="D90" t="n">
-        <v>8.280488437112332</v>
+        <v>8.347245409015013</v>
       </c>
       <c r="E90" t="n">
-        <v>2.86781180872786</v>
+        <v>2.852614896988914</v>
       </c>
     </row>
     <row r="91">
@@ -1918,16 +1918,16 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>6.4324618</v>
+        <v>6.43</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.8954067283440947</v>
+        <v>-0.924499229583986</v>
       </c>
       <c r="D91" t="n">
-        <v>8.868566669608047</v>
+        <v>8.798646362098129</v>
       </c>
       <c r="E91" t="n">
-        <v>1.946726500492169</v>
+        <v>1.901743264659284</v>
       </c>
     </row>
     <row r="92">
@@ -1935,16 +1935,16 @@
         <v>41091</v>
       </c>
       <c r="B92" t="n">
-        <v>6.41769691</v>
+        <v>6.42</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.2295371579198457</v>
+        <v>-0.1555209953343684</v>
       </c>
       <c r="D92" t="n">
-        <v>9.065185946264332</v>
+        <v>9.183673469387754</v>
       </c>
       <c r="E92" t="n">
-        <v>1.712720881890628</v>
+        <v>1.743264659270993</v>
       </c>
     </row>
     <row r="93">
@@ -1952,16 +1952,16 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>6.4535096</v>
+        <v>6.45</v>
       </c>
       <c r="C93" t="n">
-        <v>0.558030248268615</v>
+        <v>0.4672897196261738</v>
       </c>
       <c r="D93" t="n">
-        <v>8.883235187591687</v>
+        <v>8.768971332209109</v>
       </c>
       <c r="E93" t="n">
-        <v>2.280308630748595</v>
+        <v>2.21870047543582</v>
       </c>
     </row>
     <row r="94">
@@ -1969,16 +1969,16 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>6.52010864</v>
+        <v>6.52</v>
       </c>
       <c r="C94" t="n">
-        <v>1.031981729755227</v>
+        <v>1.08527131782945</v>
       </c>
       <c r="D94" t="n">
-        <v>9.185122772823462</v>
+        <v>9.212730318257956</v>
       </c>
       <c r="E94" t="n">
-        <v>3.335822728955185</v>
+        <v>3.328050713153718</v>
       </c>
     </row>
     <row r="95">
@@ -1986,16 +1986,16 @@
         <v>41183</v>
       </c>
       <c r="B95" t="n">
-        <v>6.64796623</v>
+        <v>6.65</v>
       </c>
       <c r="C95" t="n">
-        <v>1.960973306726976</v>
+        <v>1.993865030674868</v>
       </c>
       <c r="D95" t="n">
-        <v>7.798889571099776</v>
+        <v>7.779578606158832</v>
       </c>
       <c r="E95" t="n">
-        <v>5.362210628956721</v>
+        <v>5.38827258320127</v>
       </c>
     </row>
     <row r="96">
@@ -2003,16 +2003,16 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>6.67309794</v>
+        <v>6.67</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3780360659262794</v>
+        <v>0.3007518796992459</v>
       </c>
       <c r="D96" t="n">
-        <v>6.369554374584085</v>
+        <v>6.379585326953752</v>
       </c>
       <c r="E96" t="n">
-        <v>5.760517784991404</v>
+        <v>5.705229793977828</v>
       </c>
     </row>
     <row r="97">
@@ -2020,16 +2020,16 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>6.6985438</v>
+        <v>6.7</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3813200439854558</v>
+        <v>0.4497751124437732</v>
       </c>
       <c r="D97" t="n">
-        <v>6.163803837928361</v>
+        <v>6.180665610142633</v>
       </c>
       <c r="E97" t="n">
-        <v>6.163803837928361</v>
+        <v>6.180665610142633</v>
       </c>
     </row>
     <row r="98">
@@ -2037,16 +2037,16 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>6.80880919</v>
+        <v>6.81</v>
       </c>
       <c r="C98" t="n">
-        <v>1.646109860474443</v>
+        <v>1.641791044776109</v>
       </c>
       <c r="D98" t="n">
-        <v>7.307654319133783</v>
+        <v>7.244094488188968</v>
       </c>
       <c r="E98" t="n">
-        <v>1.646109860474443</v>
+        <v>1.641791044776109</v>
       </c>
     </row>
     <row r="99">
@@ -2054,16 +2054,16 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>6.82922871</v>
+        <v>6.83</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2998985495141993</v>
+        <v>0.2936857562408246</v>
       </c>
       <c r="D99" t="n">
-        <v>7.025403858174673</v>
+        <v>7.053291536050166</v>
       </c>
       <c r="E99" t="n">
-        <v>1.950945069583621</v>
+        <v>1.94029850746269</v>
       </c>
     </row>
     <row r="100">
@@ -2071,16 +2071,16 @@
         <v>41334</v>
       </c>
       <c r="B100" t="n">
-        <v>6.87446579</v>
+        <v>6.87</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6624039393168912</v>
+        <v>0.5856515373352966</v>
       </c>
       <c r="D100" t="n">
-        <v>7.29064531040986</v>
+        <v>7.176287051482055</v>
       </c>
       <c r="E100" t="n">
-        <v>2.626272145895348</v>
+        <v>2.53731343283583</v>
       </c>
     </row>
     <row r="101">
@@ -2088,16 +2088,16 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>6.90336726</v>
+        <v>6.9</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4204176860119313</v>
+        <v>0.4366812227074357</v>
       </c>
       <c r="D101" t="n">
-        <v>6.133784192762559</v>
+        <v>6.153846153846154</v>
       </c>
       <c r="E101" t="n">
-        <v>3.057731144491416</v>
+        <v>2.98507462686568</v>
       </c>
     </row>
     <row r="102">
@@ -2105,16 +2105,16 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>6.91341994</v>
+        <v>6.91</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1456199506905564</v>
+        <v>0.1449275362318758</v>
       </c>
       <c r="D102" t="n">
-        <v>6.514689487912051</v>
+        <v>6.471494607087824</v>
       </c>
       <c r="E102" t="n">
-        <v>3.207803761766836</v>
+        <v>3.134328358208949</v>
       </c>
     </row>
     <row r="103">
@@ -2122,16 +2122,16 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>6.96619654</v>
+        <v>6.97</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7633935224250266</v>
+        <v>0.868306801736618</v>
       </c>
       <c r="D103" t="n">
-        <v>8.297518999646458</v>
+        <v>8.398133748055979</v>
       </c>
       <c r="E103" t="n">
-        <v>3.995685450321296</v>
+        <v>4.029850746268648</v>
       </c>
     </row>
     <row r="104">
@@ -2139,16 +2139,16 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>6.98787264</v>
+        <v>6.99</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3111611892592236</v>
+        <v>0.2869440459110528</v>
       </c>
       <c r="D104" t="n">
-        <v>8.884429071612221</v>
+        <v>8.878504672897192</v>
       </c>
       <c r="E104" t="n">
-        <v>4.319279661946829</v>
+        <v>4.32835820895523</v>
       </c>
     </row>
     <row r="105">
@@ -2156,16 +2156,16 @@
         <v>41487</v>
       </c>
       <c r="B105" t="n">
-        <v>6.98064727</v>
+        <v>6.98</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.1033987076215492</v>
+        <v>-0.1430615164520699</v>
       </c>
       <c r="D105" t="n">
-        <v>8.168232522657126</v>
+        <v>8.217054263565892</v>
       </c>
       <c r="E105" t="n">
-        <v>4.211414874976249</v>
+        <v>4.179104477611939</v>
       </c>
     </row>
     <row r="106">
@@ -2173,16 +2173,16 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>7.03405216</v>
+        <v>7.03</v>
       </c>
       <c r="C106" t="n">
-        <v>0.7650420932957314</v>
+        <v>0.7163323782234832</v>
       </c>
       <c r="D106" t="n">
-        <v>7.882437983425983</v>
+        <v>7.822085889570563</v>
       </c>
       <c r="E106" t="n">
-        <v>5.008676064788875</v>
+        <v>4.92537313432837</v>
       </c>
     </row>
     <row r="107">
@@ -2190,16 +2190,16 @@
         <v>41548</v>
       </c>
       <c r="B107" t="n">
-        <v>7.16065316</v>
+        <v>7.16</v>
       </c>
       <c r="C107" t="n">
-        <v>1.799830270237868</v>
+        <v>1.849217638691325</v>
       </c>
       <c r="D107" t="n">
-        <v>7.711936436837163</v>
+        <v>7.669172932330826</v>
       </c>
       <c r="E107" t="n">
-        <v>6.898654002978977</v>
+        <v>6.865671641791038</v>
       </c>
     </row>
     <row r="108">
@@ -2207,16 +2207,16 @@
         <v>41579</v>
       </c>
       <c r="B108" t="n">
-        <v>7.16128146</v>
+        <v>7.16</v>
       </c>
       <c r="C108" t="n">
-        <v>0.008774339239181472</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>7.315695414474921</v>
+        <v>7.346326836581718</v>
       </c>
       <c r="E108" t="n">
-        <v>6.908033653523304</v>
+        <v>6.865671641791038</v>
       </c>
     </row>
     <row r="109">
@@ -2224,16 +2224,16 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>7.19426683</v>
+        <v>7.19</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4606070880504243</v>
+        <v>0.418994413407825</v>
       </c>
       <c r="D109" t="n">
-        <v>7.400459634226775</v>
+        <v>7.313432835820888</v>
       </c>
       <c r="E109" t="n">
-        <v>7.400459634226775</v>
+        <v>7.313432835820888</v>
       </c>
     </row>
     <row r="110">
@@ -2241,16 +2241,16 @@
         <v>41640</v>
       </c>
       <c r="B110" t="n">
-        <v>7.33657515</v>
+        <v>7.34</v>
       </c>
       <c r="C110" t="n">
-        <v>1.978079536980415</v>
+        <v>2.086230876216955</v>
       </c>
       <c r="D110" t="n">
-        <v>7.751222648082456</v>
+        <v>7.782672540381785</v>
       </c>
       <c r="E110" t="n">
-        <v>1.978079536980415</v>
+        <v>2.086230876216955</v>
       </c>
     </row>
     <row r="111">
@@ -2258,16 +2258,16 @@
         <v>41671</v>
       </c>
       <c r="B111" t="n">
-        <v>7.36798979</v>
+        <v>7.37</v>
       </c>
       <c r="C111" t="n">
-        <v>0.4281921653866094</v>
+        <v>0.4087193460490468</v>
       </c>
       <c r="D111" t="n">
-        <v>7.889047253771064</v>
+        <v>7.906295754026349</v>
       </c>
       <c r="E111" t="n">
-        <v>2.41474168396949</v>
+        <v>2.503477051460368</v>
       </c>
     </row>
     <row r="112">
@@ -2275,16 +2275,16 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>7.45092444</v>
+        <v>7.45</v>
       </c>
       <c r="C112" t="n">
-        <v>1.12560755869342</v>
+        <v>1.085481682496603</v>
       </c>
       <c r="D112" t="n">
-        <v>8.385504672065579</v>
+        <v>8.44250363901018</v>
       </c>
       <c r="E112" t="n">
-        <v>3.56752975758059</v>
+        <v>3.616133518776077</v>
       </c>
     </row>
     <row r="113">
@@ -2292,16 +2292,16 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>7.55113714</v>
+        <v>7.55</v>
       </c>
       <c r="C113" t="n">
-        <v>1.344970020928038</v>
+        <v>1.342281879194629</v>
       </c>
       <c r="D113" t="n">
-        <v>9.383390099399126</v>
+        <v>9.420289855072461</v>
       </c>
       <c r="E113" t="n">
-        <v>4.960481984235776</v>
+        <v>5.006954102920713</v>
       </c>
     </row>
     <row r="114">
@@ -2309,16 +2309,16 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>7.58098105</v>
+        <v>7.58</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3952240496588377</v>
+        <v>0.3973509933774766</v>
       </c>
       <c r="D114" t="n">
-        <v>9.656018523301224</v>
+        <v>9.696092619392193</v>
       </c>
       <c r="E114" t="n">
-        <v>5.375311051675302</v>
+        <v>5.424200278164104</v>
       </c>
     </row>
     <row r="115">
@@ -2326,16 +2326,16 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>7.60454203</v>
+        <v>7.6</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3107906462844978</v>
+        <v>0.2638522427440559</v>
       </c>
       <c r="D115" t="n">
-        <v>9.163472295600773</v>
+        <v>9.038737446197986</v>
       </c>
       <c r="E115" t="n">
-        <v>5.702807661917086</v>
+        <v>5.702364394993031</v>
       </c>
     </row>
     <row r="116">
@@ -2343,16 +2343,16 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>7.63909814</v>
+        <v>7.64</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4544140838945276</v>
+        <v>0.5263157894736858</v>
       </c>
       <c r="D116" t="n">
-        <v>9.319367045590576</v>
+        <v>9.298998569384832</v>
       </c>
       <c r="E116" t="n">
-        <v>6.183136107004805</v>
+        <v>6.258692628650886</v>
       </c>
     </row>
     <row r="117">
@@ -2360,16 +2360,16 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>7.64632351</v>
+        <v>7.65</v>
       </c>
       <c r="C117" t="n">
-        <v>0.09458407088878129</v>
+        <v>0.1308900523560252</v>
       </c>
       <c r="D117" t="n">
-        <v>9.536024587015124</v>
+        <v>9.598853868194833</v>
       </c>
       <c r="E117" t="n">
-        <v>6.283568439732168</v>
+        <v>6.397774687065372</v>
       </c>
     </row>
     <row r="118">
@@ -2377,16 +2377,16 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>7.65700448</v>
+        <v>7.66</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1396876549367931</v>
+        <v>0.1307189542483655</v>
       </c>
       <c r="D118" t="n">
-        <v>8.856236857930844</v>
+        <v>8.961593172119485</v>
       </c>
       <c r="E118" t="n">
-        <v>6.432033464068776</v>
+        <v>6.536856745479835</v>
       </c>
     </row>
     <row r="119">
@@ -2394,16 +2394,16 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>7.80245427</v>
+        <v>7.8</v>
       </c>
       <c r="C119" t="n">
-        <v>1.899565167813511</v>
+        <v>1.827676240208875</v>
       </c>
       <c r="D119" t="n">
-        <v>8.962885028214384</v>
+        <v>8.93854748603351</v>
       </c>
       <c r="E119" t="n">
-        <v>8.453779299147858</v>
+        <v>8.484005563282327</v>
       </c>
     </row>
     <row r="120">
@@ -2411,16 +2411,16 @@
         <v>41944</v>
       </c>
       <c r="B120" t="n">
-        <v>7.81659086</v>
+        <v>7.82</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1811813246295424</v>
+        <v>0.2564102564102555</v>
       </c>
       <c r="D120" t="n">
-        <v>9.150728171491252</v>
+        <v>9.21787709497206</v>
       </c>
       <c r="E120" t="n">
-        <v>8.650277293092845</v>
+        <v>8.762169680111253</v>
       </c>
     </row>
     <row r="121">
@@ -2428,16 +2428,16 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>7.78203475</v>
+        <v>7.78</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.442086718096435</v>
+        <v>-0.5115089514066473</v>
       </c>
       <c r="D121" t="n">
-        <v>8.169948848005127</v>
+        <v>8.205841446453398</v>
       </c>
       <c r="E121" t="n">
-        <v>8.169948848005127</v>
+        <v>8.205841446453398</v>
       </c>
     </row>
     <row r="122">
@@ -2445,16 +2445,16 @@
         <v>42005</v>
       </c>
       <c r="B122" t="n">
-        <v>7.86779672</v>
+        <v>7.87</v>
       </c>
       <c r="C122" t="n">
-        <v>1.10205072008962</v>
+        <v>1.156812339331625</v>
       </c>
       <c r="D122" t="n">
-        <v>7.24072962027793</v>
+        <v>7.220708446866486</v>
       </c>
       <c r="E122" t="n">
-        <v>1.10205072008962</v>
+        <v>1.156812339331625</v>
       </c>
     </row>
     <row r="123">
@@ -2462,16 +2462,16 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>7.92402893</v>
+        <v>7.92</v>
       </c>
       <c r="C123" t="n">
-        <v>0.7147135596050402</v>
+        <v>0.6353240152477735</v>
       </c>
       <c r="D123" t="n">
-        <v>7.546687167708477</v>
+        <v>7.462686567164178</v>
       </c>
       <c r="E123" t="n">
-        <v>1.824640785624876</v>
+        <v>1.799485861182526</v>
       </c>
     </row>
     <row r="124">
@@ -2479,16 +2479,16 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>8.017958699999999</v>
+        <v>8.02</v>
       </c>
       <c r="C124" t="n">
-        <v>1.18537893828714</v>
+        <v>1.262626262626254</v>
       </c>
       <c r="D124" t="n">
-        <v>7.610253795567945</v>
+        <v>7.651006711409392</v>
       </c>
       <c r="E124" t="n">
-        <v>3.031648631484196</v>
+        <v>3.084832904884305</v>
       </c>
     </row>
     <row r="125">
@@ -2496,16 +2496,16 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>8.148643610000001</v>
+        <v>8.15</v>
       </c>
       <c r="C125" t="n">
-        <v>1.629902508727077</v>
+        <v>1.620947630922709</v>
       </c>
       <c r="D125" t="n">
-        <v>7.912801196986341</v>
+        <v>7.947019867549665</v>
       </c>
       <c r="E125" t="n">
-        <v>4.710964057311617</v>
+        <v>4.755784061696655</v>
       </c>
     </row>
     <row r="126">
@@ -2513,16 +2513,16 @@
         <v>42125</v>
       </c>
       <c r="B126" t="n">
-        <v>8.19450898</v>
+        <v>8.19</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5628589516875282</v>
+        <v>0.4907975460122671</v>
       </c>
       <c r="D126" t="n">
-        <v>8.092988571709991</v>
+        <v>8.047493403693927</v>
       </c>
       <c r="E126" t="n">
-        <v>5.300339091906525</v>
+        <v>5.269922879177358</v>
       </c>
     </row>
     <row r="127">
@@ -2530,16 +2530,16 @@
         <v>42156</v>
       </c>
       <c r="B127" t="n">
-        <v>8.152413360000001</v>
+        <v>8.15</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.5137052153184607</v>
+        <v>-0.4884004884004756</v>
       </c>
       <c r="D127" t="n">
-        <v>7.204527607824929</v>
+        <v>7.236842105263164</v>
       </c>
       <c r="E127" t="n">
-        <v>4.759405758243385</v>
+        <v>4.755784061696655</v>
       </c>
     </row>
     <row r="128">
@@ -2547,16 +2547,16 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>8.159638729999999</v>
+        <v>8.16</v>
       </c>
       <c r="C128" t="n">
-        <v>0.08862860211984458</v>
+        <v>0.1226993865030668</v>
       </c>
       <c r="D128" t="n">
-        <v>6.814162882321595</v>
+        <v>6.806282722513091</v>
       </c>
       <c r="E128" t="n">
-        <v>4.852252555155956</v>
+        <v>4.884318766066831</v>
       </c>
     </row>
     <row r="129">
@@ -2564,16 +2564,16 @@
         <v>42217</v>
       </c>
       <c r="B129" t="n">
-        <v>8.192309959999999</v>
+        <v>8.19</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4004004476310996</v>
+        <v>0.3676470588235281</v>
       </c>
       <c r="D129" t="n">
-        <v>7.140509413261786</v>
+        <v>7.058823529411762</v>
       </c>
       <c r="E129" t="n">
-        <v>5.272081443738075</v>
+        <v>5.269922879177358</v>
       </c>
     </row>
     <row r="130">
@@ -2581,16 +2581,16 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>8.265506070000001</v>
+        <v>8.27</v>
       </c>
       <c r="C130" t="n">
-        <v>0.8934733958723573</v>
+        <v>0.9768009768009733</v>
       </c>
       <c r="D130" t="n">
-        <v>7.946992738340408</v>
+        <v>7.963446475195823</v>
       </c>
       <c r="E130" t="n">
-        <v>6.212659484718963</v>
+        <v>6.298200514138808</v>
       </c>
     </row>
     <row r="131">
@@ -2598,16 +2598,16 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>8.39399195</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>1.554482918672639</v>
+        <v>1.45102781136639</v>
       </c>
       <c r="D131" t="n">
-        <v>7.581430913019638</v>
+        <v>7.564102564102582</v>
       </c>
       <c r="E131" t="n">
-        <v>7.863717133876835</v>
+        <v>7.840616966580982</v>
       </c>
     </row>
     <row r="132">
@@ -2615,16 +2615,16 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>8.44991001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6661676629318158</v>
+        <v>0.7151370679379987</v>
       </c>
       <c r="D132" t="n">
-        <v>8.10224254208951</v>
+        <v>8.05626598465472</v>
       </c>
       <c r="E132" t="n">
-        <v>8.582270337458976</v>
+        <v>8.611825192802037</v>
       </c>
     </row>
     <row r="133">
@@ -2632,16 +2632,16 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>8.467502209999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>0.208193933180123</v>
+        <v>0.2366863905325589</v>
       </c>
       <c r="D133" t="n">
-        <v>8.808332036810796</v>
+        <v>8.868894601542433</v>
       </c>
       <c r="E133" t="n">
-        <v>8.808332036810796</v>
+        <v>8.868894601542433</v>
       </c>
     </row>
     <row r="134">
@@ -2649,16 +2649,16 @@
         <v>42370</v>
       </c>
       <c r="B134" t="n">
-        <v>8.62143395</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>1.817912014456979</v>
+        <v>1.770956316410843</v>
       </c>
       <c r="D134" t="n">
-        <v>9.578758282916077</v>
+        <v>9.529860228716625</v>
       </c>
       <c r="E134" t="n">
-        <v>1.817912014456979</v>
+        <v>1.770956316410843</v>
       </c>
     </row>
     <row r="135">
@@ -2666,16 +2666,16 @@
         <v>42401</v>
       </c>
       <c r="B135" t="n">
-        <v>8.61954907</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.02186272041208026</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>8.777354880252798</v>
+        <v>8.838383838383823</v>
       </c>
       <c r="E135" t="n">
-        <v>1.79565184902386</v>
+        <v>1.770956316410843</v>
       </c>
     </row>
     <row r="136">
@@ -2683,16 +2683,16 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>8.61609346</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.04009038027321665</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>7.459938151090761</v>
+        <v>7.481296758104738</v>
       </c>
       <c r="E136" t="n">
-        <v>1.754841585095979</v>
+        <v>1.770956316410843</v>
       </c>
     </row>
     <row r="137">
@@ -2700,16 +2700,16 @@
         <v>42461</v>
       </c>
       <c r="B137" t="n">
-        <v>8.683634939999999</v>
+        <v>8.68</v>
       </c>
       <c r="C137" t="n">
-        <v>0.7838991105836968</v>
+        <v>0.6960556844547661</v>
       </c>
       <c r="D137" t="n">
-        <v>6.565403465964059</v>
+        <v>6.503067484662561</v>
       </c>
       <c r="E137" t="n">
-        <v>2.552496883257382</v>
+        <v>2.479338842975198</v>
       </c>
     </row>
     <row r="138">
@@ -2717,16 +2717,16 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>8.73389836</v>
+        <v>8.73</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5788292615626744</v>
+        <v>0.5760368663594528</v>
       </c>
       <c r="D138" t="n">
-        <v>6.582327035292357</v>
+        <v>6.593406593406614</v>
       </c>
       <c r="E138" t="n">
-        <v>3.146100743680824</v>
+        <v>3.069657615112154</v>
       </c>
     </row>
     <row r="139">
@@ -2734,16 +2734,16 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>8.77505154</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4711891334627349</v>
+        <v>0.572737686139746</v>
       </c>
       <c r="D139" t="n">
-        <v>7.637470678989211</v>
+        <v>7.730061349693229</v>
       </c>
       <c r="E139" t="n">
-        <v>3.63211396197558</v>
+        <v>3.659976387249109</v>
       </c>
     </row>
     <row r="140">
@@ -2751,16 +2751,16 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>8.87714912</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C140" t="n">
-        <v>1.16349835137266</v>
+        <v>1.138952164009122</v>
       </c>
       <c r="D140" t="n">
-        <v>8.793408798381952</v>
+        <v>8.823529411764719</v>
       </c>
       <c r="E140" t="n">
-        <v>4.837871899415802</v>
+        <v>4.840613931523019</v>
       </c>
     </row>
     <row r="141">
@@ -2768,16 +2768,16 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>8.85138912</v>
+        <v>8.85</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.2901832519852987</v>
+        <v>-0.337837837837851</v>
       </c>
       <c r="D141" t="n">
-        <v>8.045095500756672</v>
+        <v>8.058608058608051</v>
       </c>
       <c r="E141" t="n">
-        <v>4.533649953425889</v>
+        <v>4.486422668240841</v>
       </c>
     </row>
     <row r="142">
@@ -2785,16 +2785,16 @@
         <v>42614</v>
       </c>
       <c r="B142" t="n">
-        <v>8.86741058</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1810050352864856</v>
+        <v>0.2259887005649608</v>
       </c>
       <c r="D142" t="n">
-        <v>7.282125315770283</v>
+        <v>7.255139056831927</v>
       </c>
       <c r="E142" t="n">
-        <v>4.722861123410338</v>
+        <v>4.722550177095619</v>
       </c>
     </row>
     <row r="143">
@@ -2802,16 +2802,16 @@
         <v>42644</v>
       </c>
       <c r="B143" t="n">
-        <v>8.99495402</v>
+        <v>8.99</v>
       </c>
       <c r="C143" t="n">
-        <v>1.438339172967451</v>
+        <v>1.352874859075537</v>
       </c>
       <c r="D143" t="n">
-        <v>7.159431097619762</v>
+        <v>7.151370679380209</v>
       </c>
       <c r="E143" t="n">
-        <v>6.229131058000648</v>
+        <v>6.139315230224307</v>
       </c>
     </row>
     <row r="144">
@@ -2819,16 +2819,16 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>9.04144769</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5168861330099306</v>
+        <v>0.5561735261401468</v>
       </c>
       <c r="D144" t="n">
-        <v>7.000520470631622</v>
+        <v>6.982248520710055</v>
       </c>
       <c r="E144" t="n">
-        <v>6.778214705656405</v>
+        <v>6.729634002361262</v>
       </c>
     </row>
     <row r="145">
@@ -2836,16 +2836,16 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>9.190038940000001</v>
+        <v>9.19</v>
       </c>
       <c r="C145" t="n">
-        <v>1.643445331927817</v>
+        <v>1.65929203539823</v>
       </c>
       <c r="D145" t="n">
-        <v>8.533056290752384</v>
+        <v>8.500590318772128</v>
       </c>
       <c r="E145" t="n">
-        <v>8.533056290752384</v>
+        <v>8.500590318772128</v>
       </c>
     </row>
     <row r="146">
@@ -2853,16 +2853,16 @@
         <v>42736</v>
       </c>
       <c r="B146" t="n">
-        <v>9.41622435</v>
+        <v>9.42</v>
       </c>
       <c r="C146" t="n">
-        <v>2.461201867333984</v>
+        <v>2.502720348204579</v>
       </c>
       <c r="D146" t="n">
-        <v>9.218772707758195</v>
+        <v>9.280742459396762</v>
       </c>
       <c r="E146" t="n">
-        <v>2.461201867333984</v>
+        <v>2.502720348204579</v>
       </c>
     </row>
     <row r="147">
@@ -2870,16 +2870,16 @@
         <v>42767</v>
       </c>
       <c r="B147" t="n">
-        <v>9.492561930000001</v>
+        <v>9.49</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8107026464381217</v>
+        <v>0.7430997876857859</v>
       </c>
       <c r="D147" t="n">
-        <v>10.12828922847586</v>
+        <v>10.09280742459397</v>
       </c>
       <c r="E147" t="n">
-        <v>3.291857542444765</v>
+        <v>3.264417845484235</v>
       </c>
     </row>
     <row r="148">
@@ -2887,16 +2887,16 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>9.589004879999999</v>
+        <v>9.59</v>
       </c>
       <c r="C148" t="n">
-        <v>1.015984417180382</v>
+        <v>1.053740779768164</v>
       </c>
       <c r="D148" t="n">
-        <v>11.29179278888648</v>
+        <v>11.25290023201857</v>
       </c>
       <c r="E148" t="n">
-        <v>4.34128671929217</v>
+        <v>4.352557127312306</v>
       </c>
     </row>
     <row r="149">
@@ -2904,16 +2904,16 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>9.714349289999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C149" t="n">
-        <v>1.307168069769515</v>
+        <v>1.251303441084484</v>
       </c>
       <c r="D149" t="n">
-        <v>11.86961862309703</v>
+        <v>11.86635944700463</v>
       </c>
       <c r="E149" t="n">
-        <v>5.705202702873402</v>
+        <v>5.65832426550601</v>
       </c>
     </row>
     <row r="150">
@@ -2921,16 +2921,16 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>9.7577015</v>
+        <v>9.76</v>
       </c>
       <c r="C150" t="n">
-        <v>0.4462698293608458</v>
+        <v>0.5149330587023604</v>
       </c>
       <c r="D150" t="n">
-        <v>11.72217831946467</v>
+        <v>11.79839633447881</v>
       </c>
       <c r="E150" t="n">
-        <v>6.176933130601059</v>
+        <v>6.202393906420034</v>
       </c>
     </row>
     <row r="151">
@@ -2938,16 +2938,16 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>9.731627339999999</v>
+        <v>9.73</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.2672162086532426</v>
+        <v>-0.307377049180324</v>
       </c>
       <c r="D151" t="n">
-        <v>10.9010846903812</v>
+        <v>10.82004555808658</v>
       </c>
       <c r="E151" t="n">
-        <v>5.893211155425182</v>
+        <v>5.875952121871619</v>
       </c>
     </row>
     <row r="152">
@@ -2955,16 +2955,16 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>9.74607808</v>
+        <v>9.75</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1484925336238785</v>
+        <v>0.2055498458376048</v>
       </c>
       <c r="D152" t="n">
-        <v>9.788378546467413</v>
+        <v>9.79729729729728</v>
       </c>
       <c r="E152" t="n">
-        <v>6.050454667605565</v>
+        <v>6.093579978237229</v>
       </c>
     </row>
     <row r="153">
@@ -2972,16 +2972,16 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>9.79665565</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5189530556274802</v>
+        <v>0.512820512820511</v>
       </c>
       <c r="D153" t="n">
-        <v>10.67930148799061</v>
+        <v>10.73446327683618</v>
       </c>
       <c r="E153" t="n">
-        <v>6.600806742609944</v>
+        <v>6.637649619151276</v>
       </c>
     </row>
     <row r="154">
@@ -2989,16 +2989,16 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>9.86042737</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6509539814232523</v>
+        <v>0.6122448979591688</v>
       </c>
       <c r="D154" t="n">
-        <v>11.19849792722691</v>
+        <v>11.16121758737316</v>
       </c>
       <c r="E154" t="n">
-        <v>7.294728938330253</v>
+        <v>7.290533188248105</v>
       </c>
     </row>
     <row r="155">
@@ -3006,16 +3006,16 @@
         <v>43009</v>
       </c>
       <c r="B155" t="n">
-        <v>10.06525083</v>
+        <v>10.07</v>
       </c>
       <c r="C155" t="n">
-        <v>2.077227003599957</v>
+        <v>2.129817444219073</v>
       </c>
       <c r="D155" t="n">
-        <v>11.89885804441277</v>
+        <v>12.01334816462736</v>
       </c>
       <c r="E155" t="n">
-        <v>9.52348402127663</v>
+        <v>9.575625680087052</v>
       </c>
     </row>
     <row r="156">
@@ -3023,16 +3023,16 @@
         <v>43040</v>
       </c>
       <c r="B156" t="n">
-        <v>10.21541281</v>
+        <v>10.22</v>
       </c>
       <c r="C156" t="n">
-        <v>1.491885125728154</v>
+        <v>1.48957298907646</v>
       </c>
       <c r="D156" t="n">
-        <v>12.98426048848822</v>
+        <v>13.05309734513276</v>
       </c>
       <c r="E156" t="n">
-        <v>11.15744858856931</v>
+        <v>11.20783460282917</v>
       </c>
     </row>
     <row r="157">
@@ -3040,16 +3040,16 @@
         <v>43070</v>
       </c>
       <c r="B157" t="n">
-        <v>10.28546746</v>
+        <v>10.29</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6857740485183506</v>
+        <v>0.6849315068492956</v>
       </c>
       <c r="D157" t="n">
-        <v>11.91973752398483</v>
+        <v>11.9695321001088</v>
       </c>
       <c r="E157" t="n">
-        <v>11.91973752398483</v>
+        <v>11.9695321001088</v>
       </c>
     </row>
     <row r="158">
@@ -3057,16 +3057,16 @@
         <v>43101</v>
       </c>
       <c r="B158" t="n">
-        <v>10.39039236</v>
+        <v>10.39</v>
       </c>
       <c r="C158" t="n">
-        <v>1.020127674391569</v>
+        <v>0.9718172983479212</v>
       </c>
       <c r="D158" t="n">
-        <v>10.34563296062503</v>
+        <v>10.29723991507432</v>
       </c>
       <c r="E158" t="n">
-        <v>1.020127674391569</v>
+        <v>0.9718172983479212</v>
       </c>
     </row>
     <row r="159">
@@ -3074,16 +3074,16 @@
         <v>43132</v>
       </c>
       <c r="B159" t="n">
-        <v>10.46641579</v>
+        <v>10.47</v>
       </c>
       <c r="C159" t="n">
-        <v>0.731670444830046</v>
+        <v>0.7699711260827691</v>
       </c>
       <c r="D159" t="n">
-        <v>10.25912569421603</v>
+        <v>10.32665964172814</v>
       </c>
       <c r="E159" t="n">
-        <v>1.759262091914682</v>
+        <v>1.749271137026254</v>
       </c>
     </row>
     <row r="160">
@@ -3091,16 +3091,16 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>10.57039825</v>
+        <v>10.57</v>
       </c>
       <c r="C160" t="n">
-        <v>0.9934868066234337</v>
+        <v>0.9551098376313183</v>
       </c>
       <c r="D160" t="n">
-        <v>10.23456951249358</v>
+        <v>10.21897810218979</v>
       </c>
       <c r="E160" t="n">
-        <v>2.770226935315212</v>
+        <v>2.721088435374153</v>
       </c>
     </row>
     <row r="161">
@@ -3108,16 +3108,16 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>10.76831048</v>
+        <v>10.77</v>
       </c>
       <c r="C161" t="n">
-        <v>1.872325198343394</v>
+        <v>1.892147587511817</v>
       </c>
       <c r="D161" t="n">
-        <v>10.84952947991025</v>
+        <v>10.91658084449021</v>
       </c>
       <c r="E161" t="n">
-        <v>4.694419790619819</v>
+        <v>4.664723032069973</v>
       </c>
     </row>
     <row r="162">
@@ -3125,16 +3125,16 @@
         <v>43221</v>
       </c>
       <c r="B162" t="n">
-        <v>10.94297588</v>
+        <v>10.94</v>
       </c>
       <c r="C162" t="n">
-        <v>1.622031611406505</v>
+        <v>1.578458681522754</v>
       </c>
       <c r="D162" t="n">
-        <v>12.14706537190138</v>
+        <v>12.09016393442623</v>
       </c>
       <c r="E162" t="n">
-        <v>6.392596375002291</v>
+        <v>6.316812439261432</v>
       </c>
     </row>
     <row r="163">
@@ -3142,16 +3142,16 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>11.22884911</v>
+        <v>11.23</v>
       </c>
       <c r="C163" t="n">
-        <v>2.612390204774906</v>
+        <v>2.650822669104214</v>
       </c>
       <c r="D163" t="n">
-        <v>15.38511204437469</v>
+        <v>15.41623843782116</v>
       </c>
       <c r="E163" t="n">
-        <v>9.171986141308563</v>
+        <v>9.13508260447038</v>
       </c>
     </row>
     <row r="164">
@@ -3159,16 +3159,16 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>11.29073595</v>
+        <v>11.29</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5511414339416598</v>
+        <v>0.5342831700801298</v>
       </c>
       <c r="D164" t="n">
-        <v>15.84902006038515</v>
+        <v>15.79487179487178</v>
       </c>
       <c r="E164" t="n">
-        <v>9.773678191190349</v>
+        <v>9.7181729834791</v>
       </c>
     </row>
     <row r="165">
@@ -3176,16 +3176,16 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>11.54990674</v>
+        <v>11.55</v>
       </c>
       <c r="C165" t="n">
-        <v>2.295428669554544</v>
+        <v>2.302922940655461</v>
       </c>
       <c r="D165" t="n">
-        <v>17.89642458240328</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="E165" t="n">
-        <v>12.29345467201548</v>
+        <v>12.24489795918369</v>
       </c>
     </row>
     <row r="166">
@@ -3193,16 +3193,16 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>12.27809811</v>
+        <v>12.28</v>
       </c>
       <c r="C166" t="n">
-        <v>6.304738093495632</v>
+        <v>6.320346320346304</v>
       </c>
       <c r="D166" t="n">
-        <v>24.51892447740833</v>
+        <v>24.54361054766734</v>
       </c>
       <c r="E166" t="n">
-        <v>19.37326288522427</v>
+        <v>19.33916423712343</v>
       </c>
     </row>
     <row r="167">
@@ -3210,16 +3210,16 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>12.60575281</v>
+        <v>12.61</v>
       </c>
       <c r="C167" t="n">
-        <v>2.668611189326953</v>
+        <v>2.687296416938101</v>
       </c>
       <c r="D167" t="n">
-        <v>25.24032458712209</v>
+        <v>25.22343594836145</v>
       </c>
       <c r="E167" t="n">
-        <v>22.55887113564405</v>
+        <v>22.54616132167153</v>
       </c>
     </row>
     <row r="168">
@@ -3227,16 +3227,16 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>12.42386204</v>
+        <v>12.42</v>
       </c>
       <c r="C168" t="n">
-        <v>-1.442918743065535</v>
+        <v>-1.506740681998409</v>
       </c>
       <c r="D168" t="n">
-        <v>21.61879574595478</v>
+        <v>21.52641878669275</v>
       </c>
       <c r="E168" t="n">
-        <v>20.79044621273829</v>
+        <v>20.69970845481051</v>
       </c>
     </row>
     <row r="169">
@@ -3244,16 +3244,16 @@
         <v>43435</v>
       </c>
       <c r="B169" t="n">
-        <v>12.37359861</v>
+        <v>12.37</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.4045717011197492</v>
+        <v>-0.4025764895330131</v>
       </c>
       <c r="D169" t="n">
-        <v>20.30176224970528</v>
+        <v>20.21379980563653</v>
       </c>
       <c r="E169" t="n">
-        <v>20.30176224970528</v>
+        <v>20.21379980563653</v>
       </c>
     </row>
     <row r="170">
@@ -3261,16 +3261,16 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>12.50522596</v>
+        <v>12.51</v>
       </c>
       <c r="C170" t="n">
-        <v>1.063775819377422</v>
+        <v>1.131770412287803</v>
       </c>
       <c r="D170" t="n">
-        <v>20.35374148277111</v>
+        <v>20.40423484119345</v>
       </c>
       <c r="E170" t="n">
-        <v>1.063775819377422</v>
+        <v>1.131770412287803</v>
       </c>
     </row>
     <row r="171">
@@ -3278,16 +3278,16 @@
         <v>43497</v>
       </c>
       <c r="B171" t="n">
-        <v>12.52533133</v>
+        <v>12.53</v>
       </c>
       <c r="C171" t="n">
-        <v>0.1607757433916834</v>
+        <v>0.1598721023181371</v>
       </c>
       <c r="D171" t="n">
-        <v>19.67163909126528</v>
+        <v>19.67526265520534</v>
       </c>
       <c r="E171" t="n">
-        <v>1.226261856250721</v>
+        <v>1.29345189975747</v>
       </c>
     </row>
     <row r="172">
@@ -3295,16 +3295,16 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>12.65413135</v>
+        <v>12.65</v>
       </c>
       <c r="C172" t="n">
-        <v>1.028316270496621</v>
+        <v>0.9577015163607427</v>
       </c>
       <c r="D172" t="n">
-        <v>19.71291005994027</v>
+        <v>19.67833491012298</v>
       </c>
       <c r="E172" t="n">
-        <v>2.26718797693406</v>
+        <v>2.263540824575605</v>
       </c>
     </row>
     <row r="173">
@@ -3312,16 +3312,16 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>12.8683792</v>
+        <v>12.87</v>
       </c>
       <c r="C173" t="n">
-        <v>1.693105943617379</v>
+        <v>1.739130434782599</v>
       </c>
       <c r="D173" t="n">
-        <v>19.50230469209131</v>
+        <v>19.49860724233983</v>
       </c>
       <c r="E173" t="n">
-        <v>3.998679814941886</v>
+        <v>4.04203718674212</v>
       </c>
     </row>
     <row r="174">
@@ -3329,16 +3329,16 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>12.99058215</v>
+        <v>12.99</v>
       </c>
       <c r="C174" t="n">
-        <v>0.9496374648331862</v>
+        <v>0.9324009324009452</v>
       </c>
       <c r="D174" t="n">
-        <v>18.71160361179558</v>
+        <v>18.73857404021939</v>
       </c>
       <c r="E174" t="n">
-        <v>4.986290241396474</v>
+        <v>5.012126111560233</v>
       </c>
     </row>
     <row r="175">
@@ -3346,16 +3346,16 @@
         <v>43617</v>
       </c>
       <c r="B175" t="n">
-        <v>12.99403776</v>
+        <v>12.99</v>
       </c>
       <c r="C175" t="n">
-        <v>0.02660088639676594</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>15.72012084860939</v>
+        <v>15.67230632235084</v>
       </c>
       <c r="E175" t="n">
-        <v>5.014217525195752</v>
+        <v>5.012126111560233</v>
       </c>
     </row>
     <row r="176">
@@ -3363,16 +3363,16 @@
         <v>43647</v>
       </c>
       <c r="B176" t="n">
-        <v>13.1702739</v>
+        <v>13.17</v>
       </c>
       <c r="C176" t="n">
-        <v>1.356284653431694</v>
+        <v>1.385681293302543</v>
       </c>
       <c r="D176" t="n">
-        <v>16.64672664672491</v>
+        <v>16.651904340124</v>
       </c>
       <c r="E176" t="n">
-        <v>6.438509241411383</v>
+        <v>6.467259498787392</v>
       </c>
     </row>
     <row r="177">
@@ -3380,16 +3380,16 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>13.2833666</v>
+        <v>13.28</v>
       </c>
       <c r="C177" t="n">
-        <v>0.8586966441145982</v>
+        <v>0.8352315869400107</v>
       </c>
       <c r="D177" t="n">
-        <v>15.00843166115469</v>
+        <v>14.97835497835496</v>
       </c>
       <c r="E177" t="n">
-        <v>7.352493148312989</v>
+        <v>7.356507679870661</v>
       </c>
     </row>
     <row r="178">
@@ -3397,16 +3397,16 @@
         <v>43709</v>
       </c>
       <c r="B178" t="n">
-        <v>13.41530809</v>
+        <v>13.42</v>
       </c>
       <c r="C178" t="n">
-        <v>0.9932835099198289</v>
+        <v>1.054216867469893</v>
       </c>
       <c r="D178" t="n">
-        <v>9.262102076491718</v>
+        <v>9.283387622149842</v>
       </c>
       <c r="E178" t="n">
-        <v>8.418807760242997</v>
+        <v>8.488278092158463</v>
       </c>
     </row>
     <row r="179">
@@ -3414,16 +3414,16 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>13.68390327</v>
+        <v>13.68</v>
       </c>
       <c r="C179" t="n">
-        <v>2.002154391073696</v>
+        <v>1.937406855439638</v>
       </c>
       <c r="D179" t="n">
-        <v>8.552844691232675</v>
+        <v>8.485329103885796</v>
       </c>
       <c r="E179" t="n">
-        <v>10.58951968056445</v>
+        <v>10.59013742926436</v>
       </c>
     </row>
     <row r="180">
@@ -3431,16 +3431,16 @@
         <v>43770</v>
       </c>
       <c r="B180" t="n">
-        <v>13.73605157</v>
+        <v>13.74</v>
       </c>
       <c r="C180" t="n">
-        <v>0.381092287566287</v>
+        <v>0.4385964912280826</v>
       </c>
       <c r="D180" t="n">
-        <v>10.56184885002154</v>
+        <v>10.6280193236715</v>
       </c>
       <c r="E180" t="n">
-        <v>11.01096781092368</v>
+        <v>11.0751818916734</v>
       </c>
     </row>
     <row r="181">
@@ -3448,16 +3448,16 @@
         <v>43800</v>
       </c>
       <c r="B181" t="n">
-        <v>13.83814915</v>
+        <v>13.84</v>
       </c>
       <c r="C181" t="n">
-        <v>0.7432818629116378</v>
+        <v>0.727802037845704</v>
       </c>
       <c r="D181" t="n">
-        <v>11.83609220050494</v>
+        <v>11.88358932902183</v>
       </c>
       <c r="E181" t="n">
-        <v>11.83609220050494</v>
+        <v>11.88358932902183</v>
       </c>
     </row>
     <row r="182">
@@ -3465,16 +3465,16 @@
         <v>43831</v>
       </c>
       <c r="B182" t="n">
-        <v>14.02506627</v>
+        <v>14.03</v>
       </c>
       <c r="C182" t="n">
-        <v>1.350737862223439</v>
+        <v>1.37283236994219</v>
       </c>
       <c r="D182" t="n">
-        <v>12.1536413245267</v>
+        <v>12.15027977617906</v>
       </c>
       <c r="E182" t="n">
-        <v>1.350737862223439</v>
+        <v>1.37283236994219</v>
       </c>
     </row>
     <row r="183">
@@ -3482,16 +3482,16 @@
         <v>43862</v>
       </c>
       <c r="B183" t="n">
-        <v>14.07438725</v>
+        <v>14.07</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3516630798779063</v>
+        <v>0.2851033499643663</v>
       </c>
       <c r="D183" t="n">
-        <v>12.36738477560097</v>
+        <v>12.29050279329609</v>
       </c>
       <c r="E183" t="n">
-        <v>1.70715098846872</v>
+        <v>1.661849710982666</v>
       </c>
     </row>
     <row r="184">
@@ -3499,16 +3499,16 @@
         <v>43891</v>
       </c>
       <c r="B184" t="n">
-        <v>14.15480873</v>
+        <v>14.15</v>
       </c>
       <c r="C184" t="n">
-        <v>0.5714030641014167</v>
+        <v>0.5685856432125158</v>
       </c>
       <c r="D184" t="n">
-        <v>11.85918921254123</v>
+        <v>11.85770750988142</v>
       </c>
       <c r="E184" t="n">
-        <v>2.28830876562709</v>
+        <v>2.239884393063596</v>
       </c>
     </row>
     <row r="185">
@@ -3516,16 +3516,16 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>14.2757551</v>
+        <v>14.28</v>
       </c>
       <c r="C185" t="n">
-        <v>0.8544542869284077</v>
+        <v>0.9187279151943395</v>
       </c>
       <c r="D185" t="n">
-        <v>10.93669900557483</v>
+        <v>10.95571095571095</v>
       </c>
       <c r="E185" t="n">
-        <v>3.162315604901544</v>
+        <v>3.179190751445082</v>
       </c>
     </row>
     <row r="186">
@@ -3533,16 +3533,16 @@
         <v>43952</v>
       </c>
       <c r="B186" t="n">
-        <v>14.47021172</v>
+        <v>14.47</v>
       </c>
       <c r="C186" t="n">
-        <v>1.362145950514382</v>
+        <v>1.330532212885172</v>
       </c>
       <c r="D186" t="n">
-        <v>11.39001742119772</v>
+        <v>11.39337952270978</v>
       </c>
       <c r="E186" t="n">
-        <v>4.567536909370573</v>
+        <v>4.552023121387294</v>
       </c>
     </row>
     <row r="187">
@@ -3550,16 +3550,16 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>14.63419615</v>
+        <v>14.63</v>
       </c>
       <c r="C187" t="n">
-        <v>1.13325522233616</v>
+        <v>1.105736005528679</v>
       </c>
       <c r="D187" t="n">
-        <v>12.6223920562164</v>
+        <v>12.6250962278676</v>
       </c>
       <c r="E187" t="n">
-        <v>5.752553982264308</v>
+        <v>5.708092485549132</v>
       </c>
     </row>
     <row r="188">
@@ -3567,16 +3567,16 @@
         <v>44013</v>
       </c>
       <c r="B188" t="n">
-        <v>14.71964397</v>
+        <v>14.72</v>
       </c>
       <c r="C188" t="n">
-        <v>0.5838914493434544</v>
+        <v>0.6151742993848242</v>
       </c>
       <c r="D188" t="n">
-        <v>11.76414463179842</v>
+        <v>11.76917236142749</v>
       </c>
       <c r="E188" t="n">
-        <v>6.37003410242909</v>
+        <v>6.358381502890187</v>
       </c>
     </row>
     <row r="189">
@@ -3584,16 +3584,16 @@
         <v>44044</v>
       </c>
       <c r="B189" t="n">
-        <v>14.84687326</v>
+        <v>14.85</v>
       </c>
       <c r="C189" t="n">
-        <v>0.8643503216470894</v>
+        <v>0.8831521739130377</v>
       </c>
       <c r="D189" t="n">
-        <v>11.77040961889888</v>
+        <v>11.82228915662651</v>
       </c>
       <c r="E189" t="n">
-        <v>7.289443834329545</v>
+        <v>7.297687861271673</v>
       </c>
     </row>
     <row r="190">
@@ -3601,16 +3601,16 @@
         <v>44075</v>
       </c>
       <c r="B190" t="n">
-        <v>14.99138061</v>
+        <v>14.99</v>
       </c>
       <c r="C190" t="n">
-        <v>0.9733184049555144</v>
+        <v>0.9427609427609562</v>
       </c>
       <c r="D190" t="n">
-        <v>11.74831401132586</v>
+        <v>11.69895678092399</v>
       </c>
       <c r="E190" t="n">
-        <v>8.333711737743489</v>
+        <v>8.309248554913307</v>
       </c>
     </row>
     <row r="191">
@@ -3618,16 +3618,16 @@
         <v>44105</v>
       </c>
       <c r="B191" t="n">
-        <v>15.3108675</v>
+        <v>15.31</v>
       </c>
       <c r="C191" t="n">
-        <v>2.131137206848632</v>
+        <v>2.134756504336233</v>
       </c>
       <c r="D191" t="n">
-        <v>11.88962095023638</v>
+        <v>11.91520467836258</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64245177614667</v>
+        <v>10.62138728323701</v>
       </c>
     </row>
     <row r="192">
@@ -3635,16 +3635,16 @@
         <v>44136</v>
       </c>
       <c r="B192" t="n">
-        <v>15.66271148</v>
+        <v>15.66</v>
       </c>
       <c r="C192" t="n">
-        <v>2.298001599190891</v>
+        <v>2.286087524493796</v>
       </c>
       <c r="D192" t="n">
-        <v>14.02630079089022</v>
+        <v>13.97379912663754</v>
       </c>
       <c r="E192" t="n">
-        <v>13.18501708734654</v>
+        <v>13.15028901734103</v>
       </c>
     </row>
     <row r="193">
@@ -3652,16 +3652,16 @@
         <v>44166</v>
       </c>
       <c r="B193" t="n">
-        <v>15.85842469</v>
+        <v>15.86</v>
       </c>
       <c r="C193" t="n">
-        <v>1.249548714792503</v>
+        <v>1.277139208173694</v>
       </c>
       <c r="D193" t="n">
-        <v>14.59931901369917</v>
+        <v>14.59537572254335</v>
       </c>
       <c r="E193" t="n">
-        <v>14.59931901369917</v>
+        <v>14.59537572254335</v>
       </c>
     </row>
     <row r="194">
@@ -3669,16 +3669,16 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>16.12513498</v>
+        <v>16.13</v>
       </c>
       <c r="C194" t="n">
-        <v>1.681820831599889</v>
+        <v>1.702395964691039</v>
       </c>
       <c r="D194" t="n">
-        <v>14.97368119031355</v>
+        <v>14.96792587312901</v>
       </c>
       <c r="E194" t="n">
-        <v>1.681820831599889</v>
+        <v>1.702395964691039</v>
       </c>
     </row>
     <row r="195">
@@ -3686,16 +3686,16 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>16.27152721</v>
+        <v>16.27</v>
       </c>
       <c r="C195" t="n">
-        <v>0.9078511912090637</v>
+        <v>0.8679479231246123</v>
       </c>
       <c r="D195" t="n">
-        <v>15.61091023696253</v>
+        <v>15.636105188344</v>
       </c>
       <c r="E195" t="n">
-        <v>2.604940453262627</v>
+        <v>2.585119798234548</v>
       </c>
     </row>
     <row r="196">
@@ -3703,16 +3703,16 @@
         <v>44256</v>
       </c>
       <c r="B196" t="n">
-        <v>16.44650676</v>
+        <v>16.45</v>
       </c>
       <c r="C196" t="n">
-        <v>1.075372629389459</v>
+        <v>1.106330669944677</v>
       </c>
       <c r="D196" t="n">
-        <v>16.19024370949589</v>
+        <v>16.25441696113072</v>
       </c>
       <c r="E196" t="n">
-        <v>3.70832589929837</v>
+        <v>3.720050441361922</v>
       </c>
     </row>
     <row r="197">
@@ -3720,16 +3720,16 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>16.72264145</v>
+        <v>16.72</v>
       </c>
       <c r="C197" t="n">
-        <v>1.678986875630017</v>
+        <v>1.641337386018238</v>
       </c>
       <c r="D197" t="n">
-        <v>17.14015358809286</v>
+        <v>17.08683473389356</v>
       </c>
       <c r="E197" t="n">
-        <v>5.449575080083191</v>
+        <v>5.422446406052961</v>
       </c>
     </row>
     <row r="198">
@@ -3737,16 +3737,16 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>16.8712327</v>
+        <v>16.87</v>
       </c>
       <c r="C198" t="n">
-        <v>0.8885632718029557</v>
+        <v>0.8971291866028741</v>
       </c>
       <c r="D198" t="n">
-        <v>16.59285314175072</v>
+        <v>16.58604008293021</v>
       </c>
       <c r="E198" t="n">
-        <v>6.386561274517111</v>
+        <v>6.368221941992447</v>
       </c>
     </row>
     <row r="199">
@@ -3754,16 +3754,16 @@
         <v>44348</v>
       </c>
       <c r="B199" t="n">
-        <v>17.1988874</v>
+        <v>17.2</v>
       </c>
       <c r="C199" t="n">
-        <v>1.942091048272965</v>
+        <v>1.956135151155891</v>
       </c>
       <c r="D199" t="n">
-        <v>17.52533055941035</v>
+        <v>17.56664388243334</v>
       </c>
       <c r="E199" t="n">
-        <v>8.452685157594942</v>
+        <v>8.448928121059263</v>
       </c>
     </row>
     <row r="200">
@@ -3771,16 +3771,16 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>17.50926405</v>
+        <v>17.51</v>
       </c>
       <c r="C200" t="n">
-        <v>1.804632141495377</v>
+        <v>1.80232558139537</v>
       </c>
       <c r="D200" t="n">
-        <v>18.95168175049275</v>
+        <v>18.9538043478261</v>
       </c>
       <c r="E200" t="n">
-        <v>10.40985717226368</v>
+        <v>10.40353089533419</v>
       </c>
     </row>
     <row r="201">
@@ -3788,16 +3788,16 @@
         <v>44409</v>
       </c>
       <c r="B201" t="n">
-        <v>17.7052914</v>
+        <v>17.71</v>
       </c>
       <c r="C201" t="n">
-        <v>1.119563617523944</v>
+        <v>1.142204454597362</v>
       </c>
       <c r="D201" t="n">
-        <v>19.25266074508134</v>
+        <v>19.25925925925927</v>
       </c>
       <c r="E201" t="n">
-        <v>11.64596576332451</v>
+        <v>11.66456494325347</v>
       </c>
     </row>
     <row r="202">
@@ -3805,16 +3805,16 @@
         <v>44440</v>
       </c>
       <c r="B202" t="n">
-        <v>17.92707877</v>
+        <v>17.93</v>
       </c>
       <c r="C202" t="n">
-        <v>1.252661506604746</v>
+        <v>1.242236024844723</v>
       </c>
       <c r="D202" t="n">
-        <v>19.58257372267465</v>
+        <v>19.61307538358905</v>
       </c>
       <c r="E202" t="n">
-        <v>13.04451180011879</v>
+        <v>13.05170239596469</v>
       </c>
     </row>
     <row r="203">
@@ -3822,16 +3822,16 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>18.35620276</v>
+        <v>18.36</v>
       </c>
       <c r="C203" t="n">
-        <v>2.393719554120066</v>
+        <v>2.398215281650873</v>
       </c>
       <c r="D203" t="n">
-        <v>19.89002425891282</v>
+        <v>19.92161985630305</v>
       </c>
       <c r="E203" t="n">
-        <v>15.7504803839378</v>
+        <v>15.76292559899117</v>
       </c>
     </row>
     <row r="204">
@@ -3839,16 +3839,16 @@
         <v>44501</v>
       </c>
       <c r="B204" t="n">
-        <v>19.00083118</v>
+        <v>19</v>
       </c>
       <c r="C204" t="n">
-        <v>3.511774349130148</v>
+        <v>3.485838779956429</v>
       </c>
       <c r="D204" t="n">
-        <v>21.31252755477557</v>
+        <v>21.32822477650065</v>
       </c>
       <c r="E204" t="n">
-        <v>19.81537606305586</v>
+        <v>19.79823455233291</v>
       </c>
     </row>
     <row r="205">
@@ -3856,16 +3856,16 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>21.58028731</v>
+        <v>21.58</v>
       </c>
       <c r="C205" t="n">
-        <v>13.57549101701983</v>
+        <v>13.57894736842105</v>
       </c>
       <c r="D205" t="n">
-        <v>36.08090167750451</v>
+        <v>36.0655737704918</v>
       </c>
       <c r="E205" t="n">
-        <v>36.08090167750451</v>
+        <v>36.0655737704918</v>
       </c>
     </row>
     <row r="206">
@@ -3873,16 +3873,16 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>23.97659609</v>
+        <v>23.98</v>
       </c>
       <c r="C206" t="n">
-        <v>11.10415605490844</v>
+        <v>11.12140871177017</v>
       </c>
       <c r="D206" t="n">
-        <v>48.69082410620542</v>
+        <v>48.6670799752015</v>
       </c>
       <c r="E206" t="n">
-        <v>11.10415605490844</v>
+        <v>11.12140871177017</v>
       </c>
     </row>
     <row r="207">
@@ -3890,16 +3890,16 @@
         <v>44593</v>
       </c>
       <c r="B207" t="n">
-        <v>25.1295134</v>
+        <v>25.13</v>
       </c>
       <c r="C207" t="n">
-        <v>4.808511206813249</v>
+        <v>4.795663052543775</v>
       </c>
       <c r="D207" t="n">
-        <v>54.43856667956864</v>
+        <v>54.45605408727721</v>
       </c>
       <c r="E207" t="n">
-        <v>16.44661185004399</v>
+        <v>16.4504170528267</v>
       </c>
     </row>
     <row r="208">
@@ -3907,16 +3907,16 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>26.50264734</v>
+        <v>26.5</v>
       </c>
       <c r="C208" t="n">
-        <v>5.4642281294631</v>
+        <v>5.451651412654202</v>
       </c>
       <c r="D208" t="n">
-        <v>61.14453802711355</v>
+        <v>61.09422492401217</v>
       </c>
       <c r="E208" t="n">
-        <v>22.80952037056081</v>
+        <v>22.79888785912883</v>
       </c>
     </row>
     <row r="209">
@@ -3924,16 +3924,16 @@
         <v>44652</v>
       </c>
       <c r="B209" t="n">
-        <v>28.42365261</v>
+        <v>28.42</v>
       </c>
       <c r="C209" t="n">
-        <v>7.248352382898227</v>
+        <v>7.245283018867932</v>
       </c>
       <c r="D209" t="n">
-        <v>69.97107003092505</v>
+        <v>69.97607655502394</v>
       </c>
       <c r="E209" t="n">
-        <v>31.71118716676624</v>
+        <v>31.69601482854496</v>
       </c>
     </row>
     <row r="210">
@@ -3941,16 +3941,16 @@
         <v>44682</v>
       </c>
       <c r="B210" t="n">
-        <v>29.27090546</v>
+        <v>29.27</v>
       </c>
       <c r="C210" t="n">
-        <v>2.980802156658502</v>
+        <v>2.990851513018988</v>
       </c>
       <c r="D210" t="n">
-        <v>73.49595006178772</v>
+        <v>73.50326022525191</v>
       </c>
       <c r="E210" t="n">
-        <v>35.63723707439372</v>
+        <v>35.63484708063023</v>
       </c>
     </row>
     <row r="211">
@@ -3958,16 +3958,16 @@
         <v>44713</v>
       </c>
       <c r="B211" t="n">
-        <v>30.72037698</v>
+        <v>30.72</v>
       </c>
       <c r="C211" t="n">
-        <v>4.951918969437985</v>
+        <v>4.953877690468045</v>
       </c>
       <c r="D211" t="n">
-        <v>78.61839702491453</v>
+        <v>78.6046511627907</v>
       </c>
       <c r="E211" t="n">
-        <v>42.35388314670219</v>
+        <v>42.35403151065802</v>
       </c>
     </row>
     <row r="212">
@@ -3975,16 +3975,16 @@
         <v>44743</v>
       </c>
       <c r="B212" t="n">
-        <v>31.44699761</v>
+        <v>31.45</v>
       </c>
       <c r="C212" t="n">
-        <v>2.365272504543325</v>
+        <v>2.376302083333326</v>
       </c>
       <c r="D212" t="n">
-        <v>79.60205249174939</v>
+        <v>79.61165048543688</v>
       </c>
       <c r="E212" t="n">
-        <v>45.72094040392089</v>
+        <v>45.73679332715479</v>
       </c>
     </row>
     <row r="213">
@@ -3992,16 +3992,16 @@
         <v>44774</v>
       </c>
       <c r="B213" t="n">
-        <v>31.90627966</v>
+        <v>31.91</v>
       </c>
       <c r="C213" t="n">
-        <v>1.460495706763276</v>
+        <v>1.462639109697927</v>
       </c>
       <c r="D213" t="n">
-        <v>80.20759409811238</v>
+        <v>80.18068887634104</v>
       </c>
       <c r="E213" t="n">
-        <v>47.84918848237523</v>
+        <v>47.86839666357741</v>
       </c>
     </row>
     <row r="214">
@@ -4009,16 +4009,16 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>32.88767303</v>
+        <v>32.89</v>
       </c>
       <c r="C214" t="n">
-        <v>3.075862746951175</v>
+        <v>3.071137574428073</v>
       </c>
       <c r="D214" t="n">
-        <v>83.45249358214318</v>
+        <v>83.43558282208589</v>
       </c>
       <c r="E214" t="n">
-        <v>52.39682659257423</v>
+        <v>52.40963855421688</v>
       </c>
     </row>
     <row r="215">
@@ -4026,16 +4026,16 @@
         <v>44835</v>
       </c>
       <c r="B215" t="n">
-        <v>34.05347034</v>
+        <v>34.05</v>
       </c>
       <c r="C215" t="n">
-        <v>3.544785029140129</v>
+        <v>3.526907874733953</v>
       </c>
       <c r="D215" t="n">
-        <v>85.51478639256433</v>
+        <v>85.45751633986927</v>
       </c>
       <c r="E215" t="n">
-        <v>57.79896648651244</v>
+        <v>57.7849860982391</v>
       </c>
     </row>
     <row r="216">
@@ -4043,16 +4043,16 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>35.035492</v>
+        <v>35.04</v>
       </c>
       <c r="C216" t="n">
-        <v>2.883763828459207</v>
+        <v>2.907488986784146</v>
       </c>
       <c r="D216" t="n">
-        <v>84.38925996499486</v>
+        <v>84.42105263157896</v>
       </c>
       <c r="E216" t="n">
-        <v>62.34951600373295</v>
+        <v>62.37256719184432</v>
       </c>
     </row>
     <row r="217">
@@ -4060,16 +4060,16 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>35.44985111</v>
+        <v>35.45</v>
       </c>
       <c r="C217" t="n">
-        <v>1.182683862410161</v>
+        <v>1.170091324200917</v>
       </c>
       <c r="D217" t="n">
-        <v>64.26959753021009</v>
+        <v>64.27247451343841</v>
       </c>
       <c r="E217" t="n">
-        <v>64.26959753021009</v>
+        <v>64.27247451343841</v>
       </c>
     </row>
     <row r="218">
@@ -4077,16 +4077,16 @@
         <v>44927</v>
       </c>
       <c r="B218" t="n">
-        <v>37.80689159</v>
+        <v>37.81</v>
       </c>
       <c r="C218" t="n">
-        <v>6.64894324291001</v>
+        <v>6.657263751763054</v>
       </c>
       <c r="D218" t="n">
-        <v>57.68248106647735</v>
+        <v>57.67306088407007</v>
       </c>
       <c r="E218" t="n">
-        <v>6.64894324291001</v>
+        <v>6.657263751763054</v>
       </c>
     </row>
     <row r="219">
@@ -4094,16 +4094,16 @@
         <v>44958</v>
       </c>
       <c r="B219" t="n">
-        <v>38.99593573</v>
+        <v>39</v>
       </c>
       <c r="C219" t="n">
-        <v>3.145046022018128</v>
+        <v>3.147315524993388</v>
       </c>
       <c r="D219" t="n">
-        <v>55.17982823336325</v>
+        <v>55.19299641862317</v>
       </c>
       <c r="E219" t="n">
-        <v>10.0031015898955</v>
+        <v>10.01410437235542</v>
       </c>
     </row>
     <row r="220">
@@ -4111,16 +4111,16 @@
         <v>44986</v>
       </c>
       <c r="B220" t="n">
-        <v>39.88873981</v>
+        <v>39.89</v>
       </c>
       <c r="C220" t="n">
-        <v>2.289479822157858</v>
+        <v>2.282051282051278</v>
       </c>
       <c r="D220" t="n">
-        <v>50.50851070940598</v>
+        <v>50.52830188679245</v>
       </c>
       <c r="E220" t="n">
-        <v>12.52160040454397</v>
+        <v>12.52468265162199</v>
       </c>
     </row>
     <row r="221">
@@ -4128,16 +4128,16 @@
         <v>45017</v>
       </c>
       <c r="B221" t="n">
-        <v>40.84028928</v>
+        <v>40.84</v>
       </c>
       <c r="C221" t="n">
-        <v>2.385508979557827</v>
+        <v>2.381549260466298</v>
       </c>
       <c r="D221" t="n">
-        <v>43.68416980170797</v>
+        <v>43.70161857846586</v>
       </c>
       <c r="E221" t="n">
-        <v>15.20581328613655</v>
+        <v>15.20451339915374</v>
       </c>
     </row>
     <row r="222">
@@ -4145,16 +4145,16 @@
         <v>45047</v>
       </c>
       <c r="B222" t="n">
-        <v>40.85788148</v>
+        <v>40.86</v>
       </c>
       <c r="C222" t="n">
-        <v>0.04307560085921036</v>
+        <v>0.04897159647403448</v>
       </c>
       <c r="D222" t="n">
-        <v>39.58530095980161</v>
+        <v>39.59685685001708</v>
       </c>
       <c r="E222" t="n">
-        <v>15.2554388824343</v>
+        <v>15.26093088857545</v>
       </c>
     </row>
     <row r="223">
@@ -4162,16 +4162,16 @@
         <v>45078</v>
       </c>
       <c r="B223" t="n">
-        <v>42.459714</v>
+        <v>42.46</v>
       </c>
       <c r="C223" t="n">
-        <v>3.920498229415292</v>
+        <v>3.915810083210958</v>
       </c>
       <c r="D223" t="n">
-        <v>38.21351875871413</v>
+        <v>38.21614583333335</v>
       </c>
       <c r="E223" t="n">
-        <v>19.77402632312495</v>
+        <v>19.7743300423131</v>
       </c>
     </row>
     <row r="224">
@@ -4179,16 +4179,16 @@
         <v>45108</v>
       </c>
       <c r="B224" t="n">
-        <v>46.48864164</v>
+        <v>46.49</v>
       </c>
       <c r="C224" t="n">
-        <v>9.488824253502969</v>
+        <v>9.491285916156379</v>
       </c>
       <c r="D224" t="n">
-        <v>47.83173330740109</v>
+        <v>47.82193958664547</v>
       </c>
       <c r="E224" t="n">
-        <v>31.13917318227066</v>
+        <v>31.14245416078985</v>
       </c>
     </row>
     <row r="225">
@@ -4196,16 +4196,16 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>50.71296836</v>
+        <v>50.71</v>
       </c>
       <c r="C225" t="n">
-        <v>9.086793184263065</v>
+        <v>9.077220907722094</v>
       </c>
       <c r="D225" t="n">
-        <v>58.94353368806395</v>
+        <v>58.9157004073958</v>
       </c>
       <c r="E225" t="n">
-        <v>43.05551863289618</v>
+        <v>43.04654442877292</v>
       </c>
     </row>
     <row r="226">
@@ -4213,16 +4213,16 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>53.12341372</v>
+        <v>53.12</v>
       </c>
       <c r="C226" t="n">
-        <v>4.753114317601748</v>
+        <v>4.752514296982846</v>
       </c>
       <c r="D226" t="n">
-        <v>61.52986461383583</v>
+        <v>61.50805716023107</v>
       </c>
       <c r="E226" t="n">
-        <v>49.8551109711558</v>
+        <v>49.84485190409025</v>
       </c>
     </row>
     <row r="227">
@@ -4230,16 +4230,16 @@
         <v>45200</v>
       </c>
       <c r="B227" t="n">
-        <v>54.9476619</v>
+        <v>54.95</v>
       </c>
       <c r="C227" t="n">
-        <v>3.433981463644531</v>
+        <v>3.44503012048194</v>
       </c>
       <c r="D227" t="n">
-        <v>61.35701105169655</v>
+        <v>61.38032305433187</v>
       </c>
       <c r="E227" t="n">
-        <v>55.00110770422923</v>
+        <v>55.00705218617772</v>
       </c>
     </row>
     <row r="228">
@@ -4247,16 +4247,16 @@
         <v>45231</v>
       </c>
       <c r="B228" t="n">
-        <v>56.75054812</v>
+        <v>56.75</v>
       </c>
       <c r="C228" t="n">
-        <v>3.281097243557141</v>
+        <v>3.275705186533218</v>
       </c>
       <c r="D228" t="n">
-        <v>61.98016605561012</v>
+        <v>61.95776255707764</v>
       </c>
       <c r="E228" t="n">
-        <v>60.08684477659574</v>
+        <v>60.08462623413258</v>
       </c>
     </row>
     <row r="229">
@@ -4264,16 +4264,16 @@
         <v>45261</v>
       </c>
       <c r="B229" t="n">
-        <v>58.41175431</v>
+        <v>58.41</v>
       </c>
       <c r="C229" t="n">
-        <v>2.927207304654322</v>
+        <v>2.925110132158593</v>
       </c>
       <c r="D229" t="n">
-        <v>64.77291859068686</v>
+        <v>64.76727785613538</v>
       </c>
       <c r="E229" t="n">
-        <v>64.77291859068686</v>
+        <v>64.76727785613538</v>
       </c>
     </row>
     <row r="230">
@@ -4281,16 +4281,16 @@
         <v>45292</v>
       </c>
       <c r="B230" t="n">
-        <v>62.32727511</v>
+        <v>62.33</v>
       </c>
       <c r="C230" t="n">
-        <v>6.703309712664574</v>
+        <v>6.711179592535532</v>
       </c>
       <c r="D230" t="n">
-        <v>64.85691494004151</v>
+        <v>64.85056863263685</v>
       </c>
       <c r="E230" t="n">
-        <v>6.703309712664574</v>
+        <v>6.711179592535532</v>
       </c>
     </row>
     <row r="231">
@@ -4298,16 +4298,16 @@
         <v>45323</v>
       </c>
       <c r="B231" t="n">
-        <v>65.15019470999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="C231" t="n">
-        <v>4.529188216583968</v>
+        <v>4.524306112626353</v>
       </c>
       <c r="D231" t="n">
-        <v>67.06919193088945</v>
+        <v>67.05128205128206</v>
       </c>
       <c r="E231" t="n">
-        <v>11.53610344287568</v>
+        <v>11.5391200136963</v>
       </c>
     </row>
     <row r="232">
@@ -4315,16 +4315,16 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>67.21068098000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="C232" t="n">
-        <v>3.162670931639977</v>
+        <v>3.161933998465072</v>
       </c>
       <c r="D232" t="n">
-        <v>68.49537313071615</v>
+        <v>68.4883429430935</v>
       </c>
       <c r="E232" t="n">
-        <v>15.0636233647474</v>
+        <v>15.06591337099812</v>
       </c>
     </row>
     <row r="233">
@@ -4332,16 +4332,16 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>69.34781897000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C233" t="n">
-        <v>3.179759465070675</v>
+        <v>3.184049992560634</v>
       </c>
       <c r="D233" t="n">
-        <v>69.80246759407871</v>
+        <v>69.8090107737512</v>
       </c>
       <c r="E233" t="n">
-        <v>18.72236981954123</v>
+        <v>18.7296695771272</v>
       </c>
     </row>
     <row r="234">
@@ -4349,16 +4349,16 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>71.6834975</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="C234" t="n">
-        <v>3.368063429666646</v>
+        <v>3.359769286229297</v>
       </c>
       <c r="D234" t="n">
-        <v>75.44594801149734</v>
+        <v>75.42829172785122</v>
       </c>
       <c r="E234" t="n">
-        <v>22.72101454026678</v>
+        <v>22.71871254922104</v>
       </c>
     </row>
     <row r="235">
@@ -4366,16 +4366,16 @@
         <v>45444</v>
       </c>
       <c r="B235" t="n">
-        <v>72.85966164</v>
+        <v>72.86</v>
       </c>
       <c r="C235" t="n">
-        <v>1.640773931266404</v>
+        <v>1.646205357142838</v>
       </c>
       <c r="D235" t="n">
-        <v>71.59715592997165</v>
+        <v>71.59679698539803</v>
       </c>
       <c r="E235" t="n">
-        <v>24.73458895502911</v>
+        <v>24.73891456942305</v>
       </c>
     </row>
     <row r="236">
@@ -4383,16 +4383,16 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>75.2097909</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="C236" t="n">
-        <v>3.225556099357152</v>
+        <v>3.225363711227014</v>
       </c>
       <c r="D236" t="n">
-        <v>61.78100337370927</v>
+        <v>61.7767261776726</v>
       </c>
       <c r="E236" t="n">
-        <v>28.75797309707613</v>
+        <v>28.76219825372368</v>
       </c>
     </row>
     <row r="237">
@@ -4400,16 +4400,16 @@
         <v>45505</v>
       </c>
       <c r="B237" t="n">
-        <v>77.07079419999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="C237" t="n">
-        <v>2.474416266459789</v>
+        <v>2.473075388911039</v>
       </c>
       <c r="D237" t="n">
-        <v>51.97452780301026</v>
+        <v>51.98185762177084</v>
       </c>
       <c r="E237" t="n">
-        <v>31.94398132775409</v>
+        <v>31.94658448895737</v>
       </c>
     </row>
     <row r="238">
@@ -4417,16 +4417,16 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>79.35840832</v>
+        <v>79.36</v>
       </c>
       <c r="C238" t="n">
-        <v>2.968198451495918</v>
+        <v>2.971324769689909</v>
       </c>
       <c r="D238" t="n">
-        <v>49.38499385276324</v>
+        <v>49.3975903614458</v>
       </c>
       <c r="E238" t="n">
-        <v>35.86034053836655</v>
+        <v>35.86714603663756</v>
       </c>
     </row>
     <row r="239">
@@ -4434,16 +4434,16 @@
         <v>45566</v>
       </c>
       <c r="B239" t="n">
-        <v>81.64382342</v>
+        <v>81.64</v>
       </c>
       <c r="C239" t="n">
-        <v>2.879865093544276</v>
+        <v>2.872983870967749</v>
       </c>
       <c r="D239" t="n">
-        <v>48.58470878812771</v>
+        <v>48.57142857142856</v>
       </c>
       <c r="E239" t="n">
-        <v>39.77293506150132</v>
+        <v>39.77058722821436</v>
       </c>
     </row>
     <row r="240">
@@ -4451,16 +4451,16 @@
         <v>45597</v>
       </c>
       <c r="B240" t="n">
-        <v>83.47592526</v>
+        <v>83.48</v>
       </c>
       <c r="C240" t="n">
-        <v>2.244017689587019</v>
+        <v>2.253797158255755</v>
       </c>
       <c r="D240" t="n">
-        <v>47.09272073194559</v>
+        <v>47.1013215859031</v>
       </c>
       <c r="E240" t="n">
-        <v>42.90946444953641</v>
+        <v>42.92073275124124</v>
       </c>
     </row>
     <row r="241">
@@ -4468,16 +4468,16 @@
         <v>45627</v>
       </c>
       <c r="B241" t="n">
-        <v>84.33417324</v>
+        <v>84.33</v>
       </c>
       <c r="C241" t="n">
-        <v>1.028138325303773</v>
+        <v>1.01820795400096</v>
       </c>
       <c r="D241" t="n">
-        <v>44.37877142402846</v>
+        <v>44.37596302003082</v>
       </c>
       <c r="E241" t="n">
-        <v>44.37877142402846</v>
+        <v>44.37596302003082</v>
       </c>
     </row>
     <row r="242">
@@ -4485,16 +4485,16 @@
         <v>45658</v>
       </c>
       <c r="B242" t="n">
-        <v>88.57829117</v>
+        <v>88.58</v>
       </c>
       <c r="C242" t="n">
-        <v>5.032500784613125</v>
+        <v>5.039724890311881</v>
       </c>
       <c r="D242" t="n">
-        <v>42.11802299020802</v>
+        <v>42.11455158029842</v>
       </c>
       <c r="E242" t="n">
-        <v>5.032500784613125</v>
+        <v>5.039724890311881</v>
       </c>
     </row>
     <row r="243">
@@ -4502,16 +4502,16 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>90.59196962999999</v>
+        <v>90.59</v>
       </c>
       <c r="C243" t="n">
-        <v>2.273331798798561</v>
+        <v>2.269135244976295</v>
       </c>
       <c r="D243" t="n">
-        <v>39.05095761148188</v>
+        <v>39.048349961627</v>
       </c>
       <c r="E243" t="n">
-        <v>7.420238024023096</v>
+        <v>7.423218309024082</v>
       </c>
     </row>
     <row r="244">
@@ -4519,16 +4519,16 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>92.82052423</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="C244" t="n">
-        <v>2.459991331573841</v>
+        <v>2.461640357655348</v>
       </c>
       <c r="D244" t="n">
-        <v>38.10382944582984</v>
+        <v>38.10444874274661</v>
       </c>
       <c r="E244" t="n">
-        <v>10.06276656777005</v>
+        <v>10.06759160441124</v>
       </c>
     </row>
     <row r="245">
@@ -4536,16 +4536,16 @@
         <v>45748</v>
       </c>
       <c r="B245" t="n">
-        <v>95.60197650000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C245" t="n">
-        <v>2.996591856244901</v>
+        <v>2.995044171514771</v>
       </c>
       <c r="D245" t="n">
-        <v>37.85866364644805</v>
+        <v>37.85147801009372</v>
       </c>
       <c r="E245" t="n">
-        <v>13.36089846749768</v>
+        <v>13.36416459148582</v>
       </c>
     </row>
     <row r="246">
@@ -4553,16 +4553,16 @@
         <v>45778</v>
       </c>
       <c r="B246" t="n">
-        <v>97.06307144</v>
+        <v>97.06</v>
       </c>
       <c r="C246" t="n">
-        <v>1.528310390109966</v>
+        <v>1.527196652719676</v>
       </c>
       <c r="D246" t="n">
-        <v>35.40504415259593</v>
+        <v>35.40736607142856</v>
       </c>
       <c r="E246" t="n">
-        <v>15.09340485709847</v>
+        <v>15.09545831851062</v>
       </c>
     </row>
     <row r="247">
@@ -4570,16 +4570,16 @@
         <v>45809</v>
       </c>
       <c r="B247" t="n">
-        <v>98.39599463</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C247" t="n">
-        <v>1.373254699470294</v>
+        <v>1.380589326189985</v>
       </c>
       <c r="D247" t="n">
-        <v>35.04865712412333</v>
+        <v>35.05352731265441</v>
       </c>
       <c r="E247" t="n">
-        <v>16.67393044807894</v>
+        <v>16.68445393098543</v>
       </c>
     </row>
     <row r="248">
@@ -4587,16 +4587,16 @@
         <v>45839</v>
       </c>
       <c r="B248" t="n">
-        <v>100.4219248</v>
+        <v>100.42</v>
       </c>
       <c r="C248" t="n">
-        <v>2.058955933743167</v>
+        <v>2.052845528455283</v>
       </c>
       <c r="D248" t="n">
-        <v>33.52240924791614</v>
+        <v>33.51947879271376</v>
       </c>
       <c r="E248" t="n">
-        <v>19.07619526217104</v>
+        <v>19.07980552591011</v>
       </c>
     </row>
     <row r="249">
@@ -4604,16 +4604,16 @@
         <v>45870</v>
       </c>
       <c r="B249" t="n">
-        <v>102.46576131</v>
+        <v>102.47</v>
       </c>
       <c r="C249" t="n">
-        <v>2.035249288509955</v>
+        <v>2.041426010754832</v>
       </c>
       <c r="D249" t="n">
-        <v>32.95018219755157</v>
+        <v>32.95705203062151</v>
       </c>
       <c r="E249" t="n">
-        <v>21.49969267902911</v>
+        <v>21.51073164947231</v>
       </c>
     </row>
     <row r="250">
@@ -4621,16 +4621,16 @@
         <v>45901</v>
       </c>
       <c r="B250" t="n">
-        <v>105.78000589</v>
+        <v>105.78</v>
       </c>
       <c r="C250" t="n">
-        <v>3.234489782370398</v>
+        <v>3.230213721089092</v>
       </c>
       <c r="D250" t="n">
-        <v>33.29401147192767</v>
+        <v>33.2913306451613</v>
       </c>
       <c r="E250" t="n">
-        <v>25.42958782434375</v>
+        <v>25.43578797580932</v>
       </c>
     </row>
     <row r="251">
@@ -4638,16 +4638,16 @@
         <v>45931</v>
       </c>
       <c r="B251" t="n">
-        <v>108.47758107</v>
+        <v>108.48</v>
       </c>
       <c r="C251" t="n">
-        <v>2.550174919450465</v>
+        <v>2.552467385138968</v>
       </c>
       <c r="D251" t="n">
-        <v>32.86685572276448</v>
+        <v>32.87604115629594</v>
       </c>
       <c r="E251" t="n">
-        <v>28.62826171461026</v>
+        <v>28.63749555318393</v>
       </c>
     </row>
     <row r="252">
@@ -4655,16 +4655,16 @@
         <v>45962</v>
       </c>
       <c r="B252" t="n">
-        <v>109.41593639</v>
+        <v>109.42</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8650223490828779</v>
+        <v>0.8665191740413025</v>
       </c>
       <c r="D252" t="n">
-        <v>31.07484109844296</v>
+        <v>31.07331097268806</v>
       </c>
       <c r="E252" t="n">
-        <v>29.74092492567843</v>
+        <v>29.75216411715877</v>
       </c>
     </row>
     <row r="253">
@@ -4672,16 +4672,16 @@
         <v>45992</v>
       </c>
       <c r="B253" t="n">
-        <v>110.38696292</v>
+        <v>110.39</v>
       </c>
       <c r="C253" t="n">
-        <v>0.8874635286571841</v>
+        <v>0.8864924145494335</v>
       </c>
       <c r="D253" t="n">
-        <v>30.89232831613635</v>
+        <v>30.90240720977113</v>
       </c>
       <c r="E253" t="n">
-        <v>30.89232831613635</v>
+        <v>30.90240720977113</v>
       </c>
     </row>
     <row r="254">
@@ -4692,13 +4692,13 @@
         <v>115.73</v>
       </c>
       <c r="C254" t="n">
-        <v>4.840279086102073</v>
+        <v>4.837394691548158</v>
       </c>
       <c r="D254" t="n">
-        <v>30.65278012407158</v>
+        <v>30.65025965229171</v>
       </c>
       <c r="E254" t="n">
-        <v>4.840279086102073</v>
+        <v>4.837394691548158</v>
       </c>
     </row>
     <row r="255">
@@ -4712,10 +4712,10 @@
         <v>2.963795040179718</v>
       </c>
       <c r="D255" t="n">
-        <v>31.53483745488579</v>
+        <v>31.53769731758471</v>
       </c>
       <c r="E255" t="n">
-        <v>7.94753007776654</v>
+        <v>7.944560195669892</v>
       </c>
     </row>
     <row r="256">
@@ -4729,10 +4729,10 @@
         <v>1.938569989929517</v>
       </c>
       <c r="D256" t="n">
-        <v>30.86545352729257</v>
+        <v>30.86619263089851</v>
       </c>
       <c r="E256" t="n">
-        <v>10.04016850072425</v>
+        <v>10.03714104538453</v>
       </c>
     </row>
     <row r="257">
@@ -4746,10 +4746,10 @@
         <v>4.182102576767921</v>
       </c>
       <c r="D257" t="n">
-        <v>32.3717402432574</v>
+        <v>32.37447698744771</v>
       </c>
       <c r="E257" t="n">
-        <v>14.6421612230728</v>
+        <v>14.63900715644533</v>
       </c>
     </row>
     <row r="258">
@@ -4763,10 +4763,10 @@
         <v>1.714737258000798</v>
       </c>
       <c r="D258" t="n">
-        <v>32.61480199456586</v>
+        <v>32.61899855759323</v>
       </c>
       <c r="E258" t="n">
-        <v>16.60797307494217</v>
+        <v>16.6047649243591</v>
       </c>
     </row>
     <row r="259">
@@ -4780,10 +4780,10 @@
         <v>0.9866376631448182</v>
       </c>
       <c r="D259" t="n">
-        <v>32.10903603221191</v>
+        <v>32.10365853658536</v>
       </c>
       <c r="E259" t="n">
-        <v>17.75847125552932</v>
+        <v>17.7552314521243</v>
       </c>
     </row>
     <row r="260">
@@ -4797,10 +4797,10 @@
         <v>1.784752673282552</v>
       </c>
       <c r="D260" t="n">
-        <v>31.75409679062435</v>
+        <v>31.75662218681538</v>
       </c>
       <c r="E260" t="n">
-        <v>19.86016871927905</v>
+        <v>19.85687109339613</v>
       </c>
     </row>
     <row r="261">
@@ -4814,10 +4814,10 @@
         <v>1.844153881036958</v>
       </c>
       <c r="D261" t="n">
-        <v>31.50734282091285</v>
+        <v>31.50190299599882</v>
       </c>
       <c r="E261" t="n">
-        <v>22.07057467253308</v>
+        <v>22.06721623335448</v>
       </c>
     </row>
     <row r="262">
@@ -4831,10 +4831,10 @@
         <v>1.840445269016699</v>
       </c>
       <c r="D262" t="n">
-        <v>29.73151102175646</v>
+        <v>29.731518245415</v>
       </c>
       <c r="E262" t="n">
-        <v>24.3172167889552</v>
+        <v>24.31379653954162</v>
       </c>
     </row>
   </sheetData>

--- a/enflasyon/enflasyon.xlsx
+++ b/enflasyon/enflasyon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Genel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Endeks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Yillik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AltKalem_Ozet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,34 +436,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>endeks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>aylik</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>yillik</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -462,7 +474,7 @@
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -475,7 +487,7 @@
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -488,7 +500,7 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -501,7 +513,7 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -514,7 +526,7 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -527,7 +539,7 @@
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -540,7 +552,7 @@
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -553,7 +565,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -566,7 +578,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -579,7 +591,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -592,7 +604,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -605,7 +617,7 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -622,7 +634,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -656,7 +668,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -690,7 +702,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -707,7 +719,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -741,7 +753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -775,7 +787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -792,7 +804,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -894,7 +906,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -928,7 +940,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -962,7 +974,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -996,7 +1008,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1030,7 +1042,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1047,7 +1059,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1064,7 +1076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -1149,7 +1161,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -1166,7 +1178,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -1183,7 +1195,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -1200,7 +1212,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -1234,7 +1246,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -1268,7 +1280,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -1319,7 +1331,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -1387,7 +1399,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -1404,7 +1416,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -1421,7 +1433,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -1489,7 +1501,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -1540,7 +1552,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -1591,7 +1603,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -1625,7 +1637,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -1710,7 +1722,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -1727,7 +1739,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -1761,7 +1773,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -1829,7 +1841,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -1863,7 +1875,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -1880,7 +1892,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -1914,7 +1926,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -1931,7 +1943,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -1999,7 +2011,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -2067,7 +2079,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -2135,7 +2147,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -2203,7 +2215,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -2254,7 +2266,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -2288,7 +2300,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -2305,7 +2317,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -2339,7 +2351,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -2424,7 +2436,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -2458,7 +2470,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -2526,7 +2538,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -2560,7 +2572,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -2628,7 +2640,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -2645,7 +2657,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -2662,7 +2674,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -2679,7 +2691,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -2696,7 +2708,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -2747,7 +2759,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -2798,7 +2810,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -2866,7 +2878,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -2883,7 +2895,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -2917,7 +2929,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -2951,7 +2963,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -2968,7 +2980,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -2985,7 +2997,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -3104,7 +3116,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -3121,7 +3133,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -3138,7 +3150,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -3155,7 +3167,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -3172,7 +3184,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -3189,7 +3201,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -3206,7 +3218,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -3274,7 +3286,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -3291,7 +3303,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -3342,7 +3354,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -3359,7 +3371,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -3393,7 +3405,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -3410,7 +3422,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -3461,7 +3473,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -3529,7 +3541,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -3546,7 +3558,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -3614,7 +3626,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -3631,7 +3643,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -3648,7 +3660,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -3682,7 +3694,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -3733,7 +3745,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -3784,7 +3796,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -3801,7 +3813,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -3818,7 +3830,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -3886,7 +3898,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -3903,7 +3915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -3920,7 +3932,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -3937,7 +3949,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -3971,7 +3983,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -3988,7 +4000,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -4107,7 +4119,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -4141,7 +4153,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -4158,7 +4170,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -4175,7 +4187,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -4192,7 +4204,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -4277,7 +4289,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -4294,7 +4306,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -4328,7 +4340,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -4345,7 +4357,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -4379,7 +4391,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -4413,7 +4425,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -4464,7 +4476,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -4515,7 +4527,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -4566,7 +4578,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -4600,7 +4612,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -4651,7 +4663,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -4685,7 +4697,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -4719,7 +4731,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -4753,7 +4765,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -4770,7 +4782,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -4787,7 +4799,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -4804,7 +4816,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -4852,79 +4864,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4968,7 +4980,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -5012,7 +5024,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -5056,7 +5068,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -5100,7 +5112,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -5144,7 +5156,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -5188,7 +5200,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -5232,7 +5244,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -5276,7 +5288,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -5320,7 +5332,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -5364,7 +5376,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -5408,7 +5420,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -5452,7 +5464,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -5540,7 +5552,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -5584,7 +5596,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -5628,7 +5640,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -5672,7 +5684,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -5716,7 +5728,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -5760,7 +5772,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -5848,7 +5860,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -5892,7 +5904,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -5936,7 +5948,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -5980,7 +5992,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -6024,7 +6036,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -6068,7 +6080,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -6112,7 +6124,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -6200,7 +6212,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -6288,7 +6300,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -6332,7 +6344,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -6376,7 +6388,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -6464,7 +6476,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -6508,7 +6520,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -6552,7 +6564,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -6596,7 +6608,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -6640,7 +6652,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -6684,7 +6696,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -6728,7 +6740,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -6816,7 +6828,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -6860,7 +6872,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -6904,7 +6916,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -6948,7 +6960,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -7036,7 +7048,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -7124,7 +7136,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -7168,7 +7180,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -7212,7 +7224,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -7256,7 +7268,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -7300,7 +7312,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -7344,7 +7356,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -7388,7 +7400,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -7432,7 +7444,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -7476,7 +7488,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -7520,7 +7532,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -7564,7 +7576,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -7608,7 +7620,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -7652,7 +7664,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -7696,7 +7708,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -7740,7 +7752,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -7784,7 +7796,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -7828,7 +7840,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -7872,7 +7884,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -7916,7 +7928,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -7960,7 +7972,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -8004,7 +8016,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -8048,7 +8060,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -8092,7 +8104,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -8136,7 +8148,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -8180,7 +8192,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -8224,7 +8236,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -8268,7 +8280,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -8312,7 +8324,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -8400,7 +8412,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -8444,7 +8456,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -8532,7 +8544,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -8576,7 +8588,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -8620,7 +8632,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -8664,7 +8676,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -8708,7 +8720,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -8752,7 +8764,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -8796,7 +8808,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -8840,7 +8852,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -8884,7 +8896,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -8928,7 +8940,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -8972,7 +8984,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -9016,7 +9028,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -9060,7 +9072,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -9104,7 +9116,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -9148,7 +9160,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -9192,7 +9204,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -9236,7 +9248,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -9280,7 +9292,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -9324,7 +9336,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -9368,7 +9380,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -9412,7 +9424,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -9456,7 +9468,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -9500,7 +9512,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -9544,7 +9556,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -9588,7 +9600,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -9676,7 +9688,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -9720,7 +9732,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -9764,7 +9776,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -9808,7 +9820,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -9852,7 +9864,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -9896,7 +9908,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -9940,7 +9952,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -9984,7 +9996,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -10028,7 +10040,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -10072,7 +10084,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -10116,7 +10128,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -10160,7 +10172,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -10204,7 +10216,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -10248,7 +10260,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -10292,7 +10304,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -10336,7 +10348,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -10380,7 +10392,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -10424,7 +10436,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -10468,7 +10480,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -10512,7 +10524,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -10600,7 +10612,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -10644,7 +10656,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -10688,7 +10700,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -10732,7 +10744,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -10776,7 +10788,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -10820,7 +10832,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -10864,7 +10876,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -10952,7 +10964,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -10996,7 +11008,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -11040,7 +11052,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -11084,7 +11096,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -11128,7 +11140,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -11172,7 +11184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -11216,7 +11228,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -11260,7 +11272,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -11304,7 +11316,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -11348,7 +11360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -11392,7 +11404,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -11436,7 +11448,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -11480,7 +11492,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -11524,7 +11536,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -11568,7 +11580,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -11612,7 +11624,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -11656,7 +11668,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -11700,7 +11712,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -11744,7 +11756,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -11788,7 +11800,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -11832,7 +11844,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -11876,7 +11888,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -11920,7 +11932,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -11964,7 +11976,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -12008,7 +12020,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -12052,7 +12064,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -12096,7 +12108,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -12140,7 +12152,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -12228,7 +12240,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -12272,7 +12284,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -12316,7 +12328,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -12360,7 +12372,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -12404,7 +12416,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -12448,7 +12460,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -12492,7 +12504,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -12536,7 +12548,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -12580,7 +12592,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -12668,7 +12680,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -12712,7 +12724,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -12756,7 +12768,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -12800,7 +12812,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -12844,7 +12856,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -12888,7 +12900,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -12932,7 +12944,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -12976,7 +12988,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -13020,7 +13032,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -13064,7 +13076,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -13108,7 +13120,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -13152,7 +13164,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -13196,7 +13208,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -13240,7 +13252,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -13284,7 +13296,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -13328,7 +13340,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -13372,7 +13384,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -13416,7 +13428,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -13504,7 +13516,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -13548,7 +13560,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -13592,7 +13604,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -13636,7 +13648,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -13680,7 +13692,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -13724,7 +13736,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -13768,7 +13780,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -13812,7 +13824,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -13856,7 +13868,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -13900,7 +13912,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -13944,7 +13956,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -13988,7 +14000,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -14032,7 +14044,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -14076,7 +14088,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -14120,7 +14132,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -14164,7 +14176,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -14208,7 +14220,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -14252,7 +14264,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -14296,7 +14308,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -14340,7 +14352,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -14384,7 +14396,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -14428,7 +14440,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -14472,7 +14484,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -14516,7 +14528,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -14560,7 +14572,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -14604,7 +14616,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -14648,7 +14660,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -14780,7 +14792,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -14824,7 +14836,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -14868,7 +14880,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -14912,7 +14924,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -14956,7 +14968,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -15000,7 +15012,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -15044,7 +15056,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -15088,7 +15100,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -15132,7 +15144,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -15176,7 +15188,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -15220,7 +15232,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -15264,7 +15276,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -15308,7 +15320,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -15352,7 +15364,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -15396,7 +15408,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -15440,7 +15452,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -15484,7 +15496,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -15528,7 +15540,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -15572,7 +15584,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -15616,7 +15628,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -15660,7 +15672,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -15704,7 +15716,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -15748,7 +15760,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -15792,7 +15804,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -15836,7 +15848,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -15880,7 +15892,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -15924,7 +15936,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -15968,7 +15980,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -16056,7 +16068,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -16100,7 +16112,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -16144,7 +16156,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -16188,7 +16200,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -16232,7 +16244,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -16276,7 +16288,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -16320,7 +16332,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -16364,7 +16376,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -16422,79 +16434,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>01. Gıda Ve Alkolsüz İçecekler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>02. Alkollü İçecekler, Tütün Ve Tütün Ürünleri</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>03. Giyim Ve Ayakkabı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>04. Konut, Su, Elektrik, Gaz Ve Diğer Yakıtlar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>05. Mobilya, Mefruşat Ve Evde Kullanılan Ekipmanlar İle Rutin Ev Bakım Ve Onarımı</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>06. Sağlık</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>07. Ulaştırma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>08. Bilgi Ve İletişim</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>09. Eğlence, Dinlence, Spor Ve Kültür</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10. Eğitim Hizmetleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>11. Lokantalar Ve Konaklama Hizmetleri</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. Sigorta Ve Finansal Hizmetler</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>13. Kişisel Bakım, Sosyal Koruma Ve Çeşitli Mal Ve Hizmetler</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -16512,7 +16524,7 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -16530,7 +16542,7 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -16548,7 +16560,7 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -16566,7 +16578,7 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -16584,7 +16596,7 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16602,7 +16614,7 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -16620,7 +16632,7 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -16638,7 +16650,7 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -16656,7 +16668,7 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -16674,7 +16686,7 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -16692,7 +16704,7 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -16710,7 +16722,7 @@
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -16754,7 +16766,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -16798,7 +16810,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -16842,7 +16854,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -16886,7 +16898,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -16930,7 +16942,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -16974,7 +16986,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -17018,7 +17030,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -17062,7 +17074,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -17106,7 +17118,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -17150,7 +17162,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -17194,7 +17206,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -17238,7 +17250,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -17282,7 +17294,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -17326,7 +17338,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -17370,7 +17382,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -17414,7 +17426,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -17458,7 +17470,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -17502,7 +17514,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -17546,7 +17558,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -17590,7 +17602,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -17634,7 +17646,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -17678,7 +17690,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -17722,7 +17734,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -17766,7 +17778,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -17854,7 +17866,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -17898,7 +17910,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -17942,7 +17954,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -17986,7 +17998,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -18030,7 +18042,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -18074,7 +18086,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -18118,7 +18130,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -18162,7 +18174,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -18206,7 +18218,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -18250,7 +18262,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -18294,7 +18306,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -18338,7 +18350,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -18382,7 +18394,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -18426,7 +18438,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -18470,7 +18482,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -18514,7 +18526,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -18558,7 +18570,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -18602,7 +18614,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -18646,7 +18658,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -18690,7 +18702,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -18734,7 +18746,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -18778,7 +18790,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -18822,7 +18834,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -18866,7 +18878,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -18910,7 +18922,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -18954,7 +18966,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -18998,7 +19010,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -19042,7 +19054,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -19086,7 +19098,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -19130,7 +19142,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -19174,7 +19186,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -19218,7 +19230,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -19262,7 +19274,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -19306,7 +19318,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -19350,7 +19362,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -19394,7 +19406,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -19438,7 +19450,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -19482,7 +19494,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -19526,7 +19538,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -19570,7 +19582,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -19614,7 +19626,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -19658,7 +19670,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -19702,7 +19714,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -19746,7 +19758,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -19790,7 +19802,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -19834,7 +19846,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -19878,7 +19890,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -19922,7 +19934,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -19966,7 +19978,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -20010,7 +20022,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -20054,7 +20066,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -20098,7 +20110,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -20142,7 +20154,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -20186,7 +20198,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -20230,7 +20242,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -20274,7 +20286,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -20318,7 +20330,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -20362,7 +20374,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -20406,7 +20418,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -20450,7 +20462,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -20494,7 +20506,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -20538,7 +20550,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -20582,7 +20594,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -20626,7 +20638,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -20670,7 +20682,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -20714,7 +20726,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -20758,7 +20770,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -20802,7 +20814,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -20846,7 +20858,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -20890,7 +20902,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -20934,7 +20946,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -20978,7 +20990,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -21022,7 +21034,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -21066,7 +21078,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -21110,7 +21122,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -21154,7 +21166,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -21198,7 +21210,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -21242,7 +21254,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -21286,7 +21298,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -21330,7 +21342,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -21374,7 +21386,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -21418,7 +21430,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -21462,7 +21474,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -21506,7 +21518,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -21550,7 +21562,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -21594,7 +21606,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -21638,7 +21650,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -21682,7 +21694,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -21726,7 +21738,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -21770,7 +21782,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -21814,7 +21826,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -21858,7 +21870,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -21902,7 +21914,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -21946,7 +21958,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -21990,7 +22002,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -22034,7 +22046,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -22078,7 +22090,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -22122,7 +22134,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -22166,7 +22178,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -22210,7 +22222,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -22254,7 +22266,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -22298,7 +22310,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -22342,7 +22354,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -22386,7 +22398,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -22430,7 +22442,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -22474,7 +22486,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -22518,7 +22530,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -22562,7 +22574,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -22606,7 +22618,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -22650,7 +22662,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -22694,7 +22706,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -22738,7 +22750,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -22782,7 +22794,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -22826,7 +22838,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -22870,7 +22882,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -22914,7 +22926,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -22958,7 +22970,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -23002,7 +23014,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -23046,7 +23058,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -23090,7 +23102,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -23134,7 +23146,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -23178,7 +23190,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -23222,7 +23234,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -23266,7 +23278,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -23310,7 +23322,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -23354,7 +23366,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -23398,7 +23410,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -23442,7 +23454,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -23486,7 +23498,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -23530,7 +23542,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -23574,7 +23586,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -23618,7 +23630,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -23662,7 +23674,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -23706,7 +23718,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -23750,7 +23762,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -23794,7 +23806,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -23838,7 +23850,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -23882,7 +23894,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -23926,7 +23938,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -23970,7 +23982,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -24014,7 +24026,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -24058,7 +24070,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -24102,7 +24114,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -24146,7 +24158,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -24190,7 +24202,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -24234,7 +24246,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -24278,7 +24290,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -24322,7 +24334,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -24366,7 +24378,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -24410,7 +24422,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -24454,7 +24466,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -24498,7 +24510,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -24542,7 +24554,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -24586,7 +24598,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -24630,7 +24642,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -24674,7 +24686,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -24718,7 +24730,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -24762,7 +24774,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -24806,7 +24818,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -24850,7 +24862,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -24894,7 +24906,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -24938,7 +24950,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -24982,7 +24994,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -25026,7 +25038,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -25070,7 +25082,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -25114,7 +25126,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -25158,7 +25170,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B206" t="n">
@@ -25202,7 +25214,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B207" t="n">
@@ -25246,7 +25258,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B208" t="n">
@@ -25290,7 +25302,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B209" t="n">
@@ -25334,7 +25346,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B210" t="n">
@@ -25378,7 +25390,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B211" t="n">
@@ -25422,7 +25434,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B212" t="n">
@@ -25466,7 +25478,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B213" t="n">
@@ -25510,7 +25522,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B214" t="n">
@@ -25554,7 +25566,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B215" t="n">
@@ -25598,7 +25610,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B216" t="n">
@@ -25642,7 +25654,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B217" t="n">
@@ -25686,7 +25698,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B218" t="n">
@@ -25730,7 +25742,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B219" t="n">
@@ -25774,7 +25786,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B220" t="n">
@@ -25818,7 +25830,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B221" t="n">
@@ -25862,7 +25874,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B222" t="n">
@@ -25906,7 +25918,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B223" t="n">
@@ -25950,7 +25962,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B224" t="n">
@@ -25994,7 +26006,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B225" t="n">
@@ -26038,7 +26050,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B226" t="n">
@@ -26082,7 +26094,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B227" t="n">
@@ -26126,7 +26138,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B228" t="n">
@@ -26170,7 +26182,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B229" t="n">
@@ -26214,7 +26226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B230" t="n">
@@ -26258,7 +26270,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B231" t="n">
@@ -26302,7 +26314,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B232" t="n">
@@ -26346,7 +26358,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B233" t="n">
@@ -26390,7 +26402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B234" t="n">
@@ -26434,7 +26446,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B235" t="n">
@@ -26478,7 +26490,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B236" t="n">
@@ -26522,7 +26534,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B237" t="n">
@@ -26566,7 +26578,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B238" t="n">
@@ -26610,7 +26622,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B239" t="n">
@@ -26654,7 +26666,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B240" t="n">
@@ -26698,7 +26710,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B241" t="n">
@@ -26742,7 +26754,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B242" t="n">
@@ -26786,7 +26798,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B243" t="n">
@@ -26830,7 +26842,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B244" t="n">
@@ -26874,7 +26886,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B245" t="n">
@@ -26918,7 +26930,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B246" t="n">
@@ -26962,7 +26974,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B247" t="n">
@@ -27006,7 +27018,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B248" t="n">
@@ -27050,7 +27062,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B249" t="n">
@@ -27094,7 +27106,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B250" t="n">
@@ -27138,7 +27150,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B251" t="n">
@@ -27182,7 +27194,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B252" t="n">
@@ -27226,7 +27238,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B253" t="n">
@@ -27270,7 +27282,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B254" t="n">
@@ -27314,7 +27326,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B255" t="n">
@@ -27358,7 +27370,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B256" t="n">
@@ -27402,7 +27414,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B257" t="n">
@@ -27446,7 +27458,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B258" t="n">
@@ -27490,7 +27502,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B259" t="n">
@@ -27534,7 +27546,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B260" t="n">
@@ -27578,7 +27590,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B261" t="n">
@@ -27622,7 +27634,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="B262" t="n">
@@ -27680,32 +27692,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Kalem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Endeks</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aylık %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Yıllık %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Yılbaşından %</t>
         </is>
